--- a/gas_prod.xlsx
+++ b/gas_prod.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\en\data-analysis\energy-commodities\natural-gas\statistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\bucom\GAS TEAM\STAFF\Stogran\Supply-Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{83714AEC-2A46-43A6-9AE7-F0FBD0993227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42448128-1C48-4906-98BE-96F3335E2FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Methods Méthodes" sheetId="22" r:id="rId1"/>
-    <sheet name="2020-21 - 103m3d 103m3j" sheetId="20" r:id="rId2"/>
-    <sheet name="2020-21 - mmcfd Mpi3j" sheetId="21" r:id="rId3"/>
+    <sheet name="2022-24 - 103m3d 103m3j" sheetId="20" r:id="rId2"/>
+    <sheet name="2022-24 - mmcfd Mpi3j" sheetId="21" r:id="rId3"/>
     <sheet name="2000+ - 103m3d 103m3j" sheetId="11" r:id="rId4"/>
     <sheet name="2000+ - mmcfd Mpi3j" sheetId="16" r:id="rId5"/>
   </sheets>
@@ -39,8 +39,8 @@
     <definedName name="_AtRisk_SimSetting_StdRecalcBehavior" hidden="1">0</definedName>
     <definedName name="_AtRisk_SimSetting_StdRecalcWithoutRiskStatic" hidden="1">0</definedName>
     <definedName name="_AtRisk_SimSetting_StdRecalcWithoutRiskStaticPercentile" hidden="1">0.5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'2020-21 - 103m3d 103m3j'!$C$1:$M$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'2020-21 - mmcfd Mpi3j'!$L$1:$M$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'2022-24 - 103m3d 103m3j'!$C$1:$M$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2022-24 - mmcfd Mpi3j'!$L$1:$M$53</definedName>
     <definedName name="RiskAfterRecalcMacro" hidden="1">""</definedName>
     <definedName name="RiskAfterSimMacro" hidden="1">"RefreshStats"</definedName>
     <definedName name="RiskBeforeRecalcMacro" hidden="1">""</definedName>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="124">
   <si>
     <t>Nova Scotia Nouvelle-Écosse</t>
   </si>
@@ -1001,7 +1001,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1221,19 +1221,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -1349,6 +1336,30 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1652,7 +1663,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1673,9 +1684,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="231"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="231" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="231" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="231" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="231" applyNumberFormat="1"/>
@@ -1697,16 +1705,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="24" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="18" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="19" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="47" fillId="0" borderId="13" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1715,19 +1714,16 @@
     <xf numFmtId="3" fontId="47" fillId="0" borderId="17" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="47" fillId="0" borderId="0" xfId="231" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="11" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="47" fillId="0" borderId="12" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1745,10 +1741,7 @@
     <xf numFmtId="3" fontId="47" fillId="0" borderId="16" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="30" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="29" xfId="231" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="24" borderId="0" xfId="231" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1799,10 +1792,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1811,8 +1804,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1826,7 +1822,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1835,7 +1840,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="231" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2443,9 +2448,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2483,9 +2488,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2518,26 +2523,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2570,26 +2558,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2767,604 +2738,604 @@
   <dimension ref="A1:M141"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="45"/>
+    <col min="1" max="16384" width="9.140625" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="38" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
+      <c r="A3" s="40"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="40" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="47"/>
+      <c r="A5" s="41"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
+      <c r="A6" s="40"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+      <c r="A7" s="39" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="42" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="47"/>
+      <c r="A9" s="41"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
+      <c r="A10" s="41" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
+      <c r="A11" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="49"/>
+      <c r="L11" s="43"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="44" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="41" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="41" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="51" t="s">
+      <c r="A15" s="45" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="46" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
+      <c r="A17" s="46" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="46" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="46" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="46" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="53"/>
+      <c r="A21" s="47"/>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
+      <c r="A22" s="41"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="41" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="47"/>
+      <c r="A24" s="41"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="48" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="53" t="s">
+      <c r="A26" s="47" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="43" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="43" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="55" t="s">
+      <c r="A29" s="49" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="49" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+      <c r="A31" s="41" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="47"/>
+      <c r="A32" s="41"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="47"/>
+      <c r="A33" s="41"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="47" t="s">
+      <c r="A34" s="41" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="47"/>
+      <c r="A35" s="41"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="48" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="49" t="s">
+      <c r="A37" s="43" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="49" t="s">
+      <c r="A38" s="43" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="47"/>
+      <c r="A39" s="41"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="47"/>
+      <c r="A40" s="41"/>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="47" t="s">
+      <c r="A41" s="41" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="47"/>
+      <c r="A42" s="41"/>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="54" t="s">
+      <c r="A43" s="48" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="43" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="49" t="s">
+      <c r="A45" s="43" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="43" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
+      <c r="A47" s="41" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="47"/>
+      <c r="A48" s="41"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="47" t="s">
+      <c r="A49" s="41" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="47"/>
+      <c r="A50" s="41"/>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="56" t="s">
+      <c r="A51" s="50" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="47"/>
+      <c r="A52" s="41"/>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="47"/>
+      <c r="A53" s="41"/>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="47" t="s">
+      <c r="A54" s="41" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="47"/>
+      <c r="A55" s="41"/>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="56" t="s">
+      <c r="A56" s="50" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="53" t="s">
+      <c r="A57" s="47" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="47"/>
+      <c r="A58" s="41"/>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="47"/>
+      <c r="A59" s="41"/>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="47" t="s">
+      <c r="A60" s="41" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="47"/>
+      <c r="A61" s="41"/>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="47" t="s">
+      <c r="A62" s="41" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="47"/>
+      <c r="A63" s="41"/>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="47"/>
+      <c r="A64" s="41"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A65" s="47" t="s">
+      <c r="A65" s="41" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A66" s="47"/>
+      <c r="A66" s="41"/>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A67" s="48" t="s">
+      <c r="A67" s="42" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A68" s="54" t="s">
+      <c r="A68" s="48" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A69" s="55" t="s">
+      <c r="A69" s="49" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A70" s="55" t="s">
+      <c r="A70" s="49" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A73" s="46" t="s">
+      <c r="A73" s="40" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A74" s="47"/>
+      <c r="A74" s="41"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="46"/>
+      <c r="A75" s="40"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A76" s="57" t="s">
+      <c r="A76" s="51" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A77" s="48" t="s">
+      <c r="A77" s="42" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A78" s="47"/>
+      <c r="A78" s="41"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A79" s="47" t="s">
+      <c r="A79" s="41" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A80" s="49" t="s">
+      <c r="A80" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="M80" s="49"/>
+      <c r="M80" s="43"/>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="58" t="s">
+      <c r="A81" s="52" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="47" t="s">
+      <c r="A82" s="41" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="47" t="s">
+      <c r="A83" s="41" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="51" t="s">
+      <c r="A84" s="45" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="52" t="s">
+      <c r="A85" s="46" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="52" t="s">
+      <c r="A86" s="46" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="52" t="s">
+      <c r="A87" s="46" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="52" t="s">
+      <c r="A88" s="46" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="52" t="s">
+      <c r="A89" s="46" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="53"/>
+      <c r="A90" s="47"/>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="47"/>
+      <c r="A91" s="41"/>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="47" t="s">
+      <c r="A92" s="41" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="47"/>
+      <c r="A93" s="41"/>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="54" t="s">
+      <c r="A94" s="48" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="53" t="s">
+      <c r="A95" s="47" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="49" t="s">
+      <c r="A96" s="43" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="49" t="s">
+      <c r="A97" s="43" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="55" t="s">
+      <c r="A98" s="49" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="55" t="s">
+      <c r="A99" s="49" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="47" t="s">
+      <c r="A100" s="41" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="47"/>
+      <c r="A101" s="41"/>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="47"/>
+      <c r="A103" s="41"/>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="47" t="s">
+      <c r="A104" s="41" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="47"/>
+      <c r="A105" s="41"/>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="54" t="s">
+      <c r="A106" s="48" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107" s="49" t="s">
+      <c r="A107" s="43" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108" s="49" t="s">
+      <c r="A108" s="43" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" s="47"/>
+      <c r="A109" s="41"/>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" s="47"/>
+      <c r="A110" s="41"/>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" s="47" t="s">
+      <c r="A111" s="41" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" s="47"/>
+      <c r="A112" s="41"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" s="54" t="s">
+      <c r="A113" s="48" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" s="49" t="s">
+      <c r="A114" s="43" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" s="49" t="s">
+      <c r="A115" s="43" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" s="49" t="s">
+      <c r="A116" s="43" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" s="47" t="s">
+      <c r="A117" s="41" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" s="47"/>
+      <c r="A118" s="41"/>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" s="47" t="s">
+      <c r="A119" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" s="47"/>
+      <c r="A120" s="41"/>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" s="56" t="s">
+      <c r="A121" s="50" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="47"/>
+      <c r="A122" s="41"/>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="47"/>
+      <c r="A123" s="41"/>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="47" t="s">
+      <c r="A124" s="41" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="47"/>
+      <c r="A125" s="41"/>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="56" t="s">
+      <c r="A126" s="50" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="53" t="s">
+      <c r="A127" s="47" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="47"/>
+      <c r="A128" s="41"/>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="47"/>
+      <c r="A129" s="41"/>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="47" t="s">
+      <c r="A130" s="41" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="47"/>
+      <c r="A131" s="41"/>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="47" t="s">
+      <c r="A132" s="41" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="47"/>
+      <c r="A133" s="41"/>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="47" t="s">
+      <c r="A134" s="41" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="47"/>
+      <c r="A135" s="41"/>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="48" t="s">
+      <c r="A136" s="42" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="54" t="s">
+      <c r="A137" s="48" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="55" t="s">
+      <c r="A138" s="49" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="55" t="s">
+      <c r="A139" s="49" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="47"/>
+      <c r="A140" s="41"/>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="47"/>
+      <c r="A141" s="41"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3442,1275 +3413,1143 @@
       <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="61" t="s">
+      <c r="C5" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="63"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="57"/>
     </row>
     <row r="6" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="64"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="66"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="60"/>
     </row>
     <row r="7" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="69" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="F7" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="71" t="s">
+      <c r="I7" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="69" t="s">
+      <c r="J7" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="73" t="s">
+      <c r="K7" s="70" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="74"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="71"/>
     </row>
     <row r="9" spans="1:17" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="74"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="72"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B10" s="14">
-        <v>2021</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="17">
+        <v>2022</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="36">
-        <v>0</v>
-      </c>
-      <c r="E10" s="27">
-        <v>343.24193548387098</v>
-      </c>
-      <c r="F10" s="26">
-        <v>186.80645751953125</v>
-      </c>
-      <c r="G10" s="27">
-        <v>9015.0999999999985</v>
-      </c>
-      <c r="H10" s="26">
-        <v>280010.125</v>
-      </c>
-      <c r="I10" s="27">
-        <v>157082.34375</v>
-      </c>
-      <c r="J10" s="27">
-        <v>169.68801612903223</v>
-      </c>
-      <c r="K10" s="29">
-        <f t="shared" ref="K10:K42" si="0">SUM(D10:J10)</f>
-        <v>446807.3051591324</v>
-      </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="16"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="17"/>
+      <c r="D10" s="37">
+        <v>0</v>
+      </c>
+      <c r="E10" s="26">
+        <v>287.63548387096779</v>
+      </c>
+      <c r="F10" s="25">
+        <v>159.48387145996094</v>
+      </c>
+      <c r="G10" s="26">
+        <v>8533.8290322580651</v>
+      </c>
+      <c r="H10" s="25">
+        <v>289498.375</v>
+      </c>
+      <c r="I10" s="26">
+        <v>170521.5625</v>
+      </c>
+      <c r="J10" s="26">
+        <v>183.65237096774194</v>
+      </c>
+      <c r="K10" s="27">
+        <f t="shared" ref="K10:K34" si="0">SUM(D10:J10)</f>
+        <v>469184.53825855674</v>
+      </c>
+      <c r="L10" s="14"/>
+      <c r="M10" s="15"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="16"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="18"/>
-      <c r="C11" s="18" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="37">
         <v>0</v>
       </c>
-      <c r="E11" s="30">
-        <v>323.24285714285713</v>
-      </c>
-      <c r="F11" s="28">
-        <v>187.46427917480469</v>
-      </c>
-      <c r="G11" s="30">
-        <v>8426.096428571429</v>
-      </c>
-      <c r="H11" s="28">
-        <v>271371.6875</v>
-      </c>
-      <c r="I11" s="30">
-        <v>157801.765625</v>
-      </c>
-      <c r="J11" s="30">
-        <v>161.07310714285714</v>
-      </c>
-      <c r="K11" s="31">
-        <f t="shared" si="0"/>
-        <v>438271.32979703194</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="16"/>
-      <c r="Q11" s="17"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="37">
-        <v>0</v>
-      </c>
-      <c r="E12" s="30">
-        <v>298.07419354838709</v>
-      </c>
-      <c r="F12" s="28">
-        <v>183.90322875976563</v>
-      </c>
-      <c r="G12" s="30">
-        <v>9076.5193548387106</v>
-      </c>
-      <c r="H12" s="28">
-        <v>285873.84375</v>
-      </c>
-      <c r="I12" s="30">
-        <v>158179.125</v>
-      </c>
-      <c r="J12" s="30">
-        <v>170.75922580645164</v>
-      </c>
-      <c r="K12" s="31">
-        <f t="shared" si="0"/>
-        <v>453782.22475295333</v>
-      </c>
-      <c r="L12" s="15"/>
-      <c r="M12" s="16"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="37">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30">
-        <v>246.09666666666666</v>
-      </c>
-      <c r="F13" s="28">
-        <v>196.46665954589844</v>
-      </c>
-      <c r="G13" s="30">
-        <v>9408.8233333333337</v>
-      </c>
-      <c r="H13" s="28">
-        <v>287414</v>
-      </c>
-      <c r="I13" s="30">
-        <v>161376.40625</v>
-      </c>
-      <c r="J13" s="30">
-        <v>189.32395</v>
-      </c>
-      <c r="K13" s="31">
-        <f t="shared" si="0"/>
-        <v>458831.11685954587</v>
-      </c>
-      <c r="L13" s="15"/>
-      <c r="M13" s="16"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="37">
-        <v>0</v>
-      </c>
-      <c r="E14" s="30">
-        <v>3.2258064516129032E-3</v>
-      </c>
-      <c r="F14" s="28">
-        <v>194.64515686035156</v>
-      </c>
-      <c r="G14" s="30">
-        <v>9204.5580645161281</v>
-      </c>
-      <c r="H14" s="28">
-        <v>282263.1875</v>
-      </c>
-      <c r="I14" s="30">
-        <v>157110.671875</v>
-      </c>
-      <c r="J14" s="30">
-        <v>191.63851612903224</v>
-      </c>
-      <c r="K14" s="31">
-        <f t="shared" si="0"/>
-        <v>448964.70433831197</v>
-      </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="16"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="37">
-        <v>0</v>
-      </c>
-      <c r="E15" s="30">
-        <v>0.21666666666666667</v>
-      </c>
-      <c r="F15" s="28">
-        <v>205.06666564941406</v>
-      </c>
-      <c r="G15" s="30">
-        <v>8761.2566666666644</v>
-      </c>
-      <c r="H15" s="28">
-        <v>279415.5625</v>
-      </c>
-      <c r="I15" s="30">
-        <v>157099.84375</v>
-      </c>
-      <c r="J15" s="30">
-        <v>166.95235</v>
-      </c>
-      <c r="K15" s="31">
-        <f t="shared" si="0"/>
-        <v>445648.89859898272</v>
-      </c>
-      <c r="L15" s="15"/>
-      <c r="M15" s="16"/>
-      <c r="Q15" s="17"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="37">
-        <v>0</v>
-      </c>
-      <c r="E16" s="30">
-        <v>6.4516129032258063E-2</v>
-      </c>
-      <c r="F16" s="28">
-        <v>212.8709716796875</v>
-      </c>
-      <c r="G16" s="30">
-        <v>8979.8000000000011</v>
-      </c>
-      <c r="H16" s="28">
-        <v>285369.125</v>
-      </c>
-      <c r="I16" s="30">
-        <v>159039.34375</v>
-      </c>
-      <c r="J16" s="30">
-        <v>49.631983870967744</v>
-      </c>
-      <c r="K16" s="31">
-        <f t="shared" si="0"/>
-        <v>453650.8362216797</v>
-      </c>
-      <c r="L16" s="15"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q16" s="17"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B17" s="20"/>
-      <c r="C17" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="37">
-        <v>0</v>
-      </c>
-      <c r="E17" s="30">
-        <v>0.2129032258064516</v>
-      </c>
-      <c r="F17" s="28">
-        <v>168.06451416015625</v>
-      </c>
-      <c r="G17" s="30">
-        <v>8929.5354838709682</v>
-      </c>
-      <c r="H17" s="28">
-        <v>289231.53125</v>
-      </c>
-      <c r="I17" s="30">
-        <v>164678.109375</v>
-      </c>
-      <c r="J17" s="30">
-        <v>30.615145161290322</v>
-      </c>
-      <c r="K17" s="31">
-        <f t="shared" si="0"/>
-        <v>463038.06867141824</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="16"/>
-      <c r="Q17" s="17"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="18"/>
-      <c r="C18" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="37">
-        <v>0</v>
-      </c>
-      <c r="E18" s="30">
-        <v>1.5933333333333333</v>
-      </c>
-      <c r="F18" s="35">
-        <v>155.19999694824219</v>
-      </c>
-      <c r="G18" s="30">
-        <v>9079.8933333333352</v>
-      </c>
-      <c r="H18" s="28">
-        <v>283808.0625</v>
-      </c>
-      <c r="I18" s="30">
-        <v>167572.828125</v>
-      </c>
-      <c r="J18" s="30">
-        <v>190.33291666666668</v>
-      </c>
-      <c r="K18" s="31">
-        <f t="shared" si="0"/>
-        <v>460807.91020528163</v>
-      </c>
-      <c r="L18" s="15"/>
-      <c r="M18" s="16"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B19" s="18"/>
-      <c r="C19" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="37">
-        <v>0</v>
-      </c>
-      <c r="E19" s="30">
-        <v>0.6967741935483871</v>
-      </c>
-      <c r="F19" s="35">
-        <v>191.67741394042969</v>
-      </c>
-      <c r="G19" s="30">
-        <v>9124.7000000000007</v>
-      </c>
-      <c r="H19" s="28">
-        <v>290234.9375</v>
-      </c>
-      <c r="I19" s="30">
-        <v>161504.5625</v>
-      </c>
-      <c r="J19" s="30">
-        <v>173.48519354838712</v>
-      </c>
-      <c r="K19" s="31">
-        <f t="shared" si="0"/>
-        <v>461230.05938168237</v>
-      </c>
-      <c r="L19" s="15"/>
-      <c r="M19" s="16"/>
-      <c r="Q19" s="17"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B20" s="18"/>
-      <c r="C20" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="37">
-        <v>0</v>
-      </c>
-      <c r="E20" s="30">
-        <v>249.09</v>
-      </c>
-      <c r="F20" s="28">
-        <v>190.19999694824219</v>
-      </c>
-      <c r="G20" s="30">
-        <v>9125.92</v>
-      </c>
-      <c r="H20" s="28">
-        <v>295358.90625</v>
-      </c>
-      <c r="I20" s="30">
-        <v>171982.53125</v>
-      </c>
-      <c r="J20" s="30">
-        <v>187.82973333333334</v>
-      </c>
-      <c r="K20" s="31">
-        <f t="shared" si="0"/>
-        <v>477094.47723028157</v>
-      </c>
-      <c r="L20" s="15"/>
-      <c r="M20" s="16"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B21" s="42"/>
-      <c r="C21" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="43">
-        <v>0</v>
-      </c>
-      <c r="E21" s="30">
-        <v>331.7161290322581</v>
-      </c>
-      <c r="F21" s="30">
-        <v>187.09677124023438</v>
-      </c>
-      <c r="G21" s="30">
-        <v>8745.1096774193556</v>
-      </c>
-      <c r="H21" s="30">
-        <v>286711.3125</v>
-      </c>
-      <c r="I21" s="30">
-        <v>170788.328125</v>
-      </c>
-      <c r="J21" s="30">
-        <v>193.85454838709677</v>
-      </c>
-      <c r="K21" s="31">
-        <f t="shared" si="0"/>
-        <v>466957.41775107896</v>
-      </c>
-      <c r="L21" s="22"/>
-      <c r="M21" s="16"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B22" s="18">
-        <v>2022</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="43">
-        <v>0</v>
-      </c>
-      <c r="E22" s="30">
-        <v>287.63548387096779</v>
-      </c>
-      <c r="F22" s="28">
-        <v>159.48387145996094</v>
-      </c>
-      <c r="G22" s="30">
-        <v>8533.8290322580651</v>
-      </c>
-      <c r="H22" s="28">
-        <v>289498.375</v>
-      </c>
-      <c r="I22" s="30">
-        <v>170521.5625</v>
-      </c>
-      <c r="J22" s="30">
-        <v>183.65237096774194</v>
-      </c>
-      <c r="K22" s="31">
-        <f t="shared" si="0"/>
-        <v>469184.53825855674</v>
-      </c>
-      <c r="L22" s="15"/>
-      <c r="M22" s="16"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B23" s="18"/>
-      <c r="C23" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="43">
-        <v>0</v>
-      </c>
-      <c r="E23" s="30">
+      <c r="E11" s="26">
         <v>277.40714285714284</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F11" s="25">
         <v>160.46427917480469</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G11" s="26">
         <v>8538.2071428571435</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H11" s="25">
         <v>296883.65625</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I11" s="26">
         <v>173246.65625</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J11" s="26">
         <v>177.44130357142856</v>
       </c>
-      <c r="K23" s="31">
+      <c r="K11" s="27">
         <f t="shared" si="0"/>
         <v>479283.83236846054</v>
       </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="16"/>
-      <c r="Q23" s="17"/>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B24" s="18"/>
-      <c r="C24" s="18" t="s">
+      <c r="L11" s="14"/>
+      <c r="M11" s="15"/>
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="43">
-        <v>0</v>
-      </c>
-      <c r="E24" s="30">
+      <c r="D12" s="37">
+        <v>0</v>
+      </c>
+      <c r="E12" s="26">
         <v>236.89999999999998</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F12" s="25">
         <v>163.32258605957031</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G12" s="26">
         <v>8877.3419354838716</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H12" s="25">
         <v>303096.3125</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I12" s="26">
         <v>173631.546875</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J12" s="26">
         <v>168.34427419354842</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K12" s="27">
         <f t="shared" si="0"/>
         <v>486173.76817073702</v>
       </c>
-      <c r="L24" s="15"/>
-      <c r="M24" s="16"/>
-      <c r="Q24" s="17"/>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B25" s="18"/>
-      <c r="C25" s="18" t="s">
+      <c r="L12" s="14"/>
+      <c r="M12" s="15"/>
+      <c r="Q12" s="16"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="37">
-        <v>0</v>
-      </c>
-      <c r="E25" s="30">
+      <c r="D13" s="32">
+        <v>0</v>
+      </c>
+      <c r="E13" s="26">
         <v>123.65</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F13" s="25">
         <v>176.33332824707031</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G13" s="26">
         <v>8708.2633333333342</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H13" s="25">
         <v>310446</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I13" s="26">
         <v>176777.96875</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J13" s="26">
         <v>169.73816666666667</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K13" s="27">
         <f t="shared" si="0"/>
         <v>496401.95357824705</v>
       </c>
-      <c r="L25" s="15"/>
-      <c r="M25" s="16"/>
-      <c r="Q25" s="17"/>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B26" s="18"/>
-      <c r="C26" s="18" t="s">
+      <c r="L13" s="14"/>
+      <c r="M13" s="15"/>
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="37">
-        <v>0</v>
-      </c>
-      <c r="E26" s="30">
+      <c r="D14" s="32">
+        <v>0</v>
+      </c>
+      <c r="E14" s="26">
         <v>0.48064516129032259</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F14" s="25">
         <v>188.38710021972656</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G14" s="26">
         <v>8871.4709677419341</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H14" s="25">
         <v>302011.3125</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I14" s="26">
         <v>174744.71875</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J14" s="26">
         <v>189.10001612903227</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K14" s="27">
         <f t="shared" si="0"/>
         <v>486005.46997925197</v>
       </c>
-      <c r="L26" s="15"/>
-      <c r="M26" s="16"/>
-      <c r="Q26" s="17"/>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B27" s="18"/>
-      <c r="C27" s="18" t="s">
+      <c r="L14" s="14"/>
+      <c r="M14" s="15"/>
+      <c r="Q14" s="16"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="37">
-        <v>0</v>
-      </c>
-      <c r="E27" s="30">
+      <c r="D15" s="32">
+        <v>0</v>
+      </c>
+      <c r="E15" s="26">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F15" s="25">
         <v>197.83332824707031</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G15" s="26">
         <v>8678.64</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H15" s="25">
         <v>298256.1875</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I15" s="26">
         <v>173099.8125</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J15" s="26">
         <v>175.05</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K15" s="27">
         <f t="shared" si="0"/>
         <v>480407.9399949137</v>
       </c>
-      <c r="L27" s="15"/>
-      <c r="M27" s="16"/>
-      <c r="Q27" s="17"/>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B28" s="18"/>
-      <c r="C28" s="18" t="s">
+      <c r="L15" s="14"/>
+      <c r="M15" s="15"/>
+      <c r="Q15" s="16"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="37">
-        <v>0</v>
-      </c>
-      <c r="E28" s="30">
+      <c r="D16" s="32">
+        <v>0</v>
+      </c>
+      <c r="E16" s="26">
         <v>0.38064516129032261</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F16" s="25">
         <v>196.19354248046875</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G16" s="26">
         <v>8622.1612903225814</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H16" s="25">
         <v>309144.09375</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I16" s="26">
         <v>177231.71875</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J16" s="26">
         <v>161.24408064516126</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K16" s="27">
         <f t="shared" si="0"/>
         <v>495355.79205860948</v>
       </c>
-      <c r="L28" s="15"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="19" t="s">
+      <c r="L16" s="14"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="Q28" s="17"/>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B29" s="20"/>
-      <c r="C29" s="20" t="s">
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B17" s="19"/>
+      <c r="C17" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="37">
-        <v>0</v>
-      </c>
-      <c r="E29" s="30">
+      <c r="D17" s="32">
+        <v>0</v>
+      </c>
+      <c r="E17" s="26">
         <v>0.40322580645161288</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F17" s="25">
         <v>200.1290283203125</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G17" s="26">
         <v>8659.6064516129027</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H17" s="25">
         <v>305343.8125</v>
       </c>
-      <c r="I29" s="30">
+      <c r="I17" s="26">
         <v>169422.3125</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J17" s="26">
         <v>156.69672580645161</v>
       </c>
-      <c r="K29" s="31">
+      <c r="K17" s="27">
         <f t="shared" si="0"/>
         <v>483782.96043154615</v>
       </c>
-      <c r="L29" s="15"/>
-      <c r="M29" s="16"/>
-      <c r="Q29" s="17"/>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B30" s="18"/>
-      <c r="C30" s="18" t="s">
+      <c r="L17" s="14"/>
+      <c r="M17" s="15"/>
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="37">
-        <v>0</v>
-      </c>
-      <c r="E30" s="30">
-        <v>0</v>
-      </c>
-      <c r="F30" s="35">
+      <c r="D18" s="32">
+        <v>0</v>
+      </c>
+      <c r="E18" s="26">
+        <v>0</v>
+      </c>
+      <c r="F18" s="31">
         <v>200.16667175292969</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G18" s="26">
         <v>8809.626666666667</v>
       </c>
-      <c r="H30" s="28">
+      <c r="H18" s="25">
         <v>307787.875</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I18" s="26">
         <v>175183.765625</v>
       </c>
-      <c r="J30" s="30">
+      <c r="J18" s="26">
         <v>136.90261666666666</v>
       </c>
-      <c r="K30" s="31">
+      <c r="K18" s="27">
         <f t="shared" si="0"/>
         <v>492118.33658008627</v>
       </c>
-      <c r="L30" s="15"/>
-      <c r="M30" s="16"/>
-      <c r="Q30" s="17"/>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B31" s="18"/>
-      <c r="C31" s="18" t="s">
+      <c r="L18" s="14"/>
+      <c r="M18" s="15"/>
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="37">
-        <v>0</v>
-      </c>
-      <c r="E31" s="30">
+      <c r="D19" s="32">
+        <v>0</v>
+      </c>
+      <c r="E19" s="26">
         <v>16.535483870967742</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F19" s="31">
         <v>184.25807189941406</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G19" s="26">
         <v>9060.4258064516125</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H19" s="25">
         <v>309619.28125</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I19" s="26">
         <v>183863.03125</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J19" s="26">
         <v>161.20404838709678</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K19" s="27">
         <f t="shared" si="0"/>
         <v>502904.73591060913</v>
       </c>
-      <c r="L31" s="15"/>
-      <c r="M31" s="16"/>
-      <c r="Q31" s="17"/>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B32" s="18"/>
-      <c r="C32" s="18" t="s">
+      <c r="L19" s="14"/>
+      <c r="M19" s="15"/>
+      <c r="Q19" s="16"/>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="37">
-        <v>0</v>
-      </c>
-      <c r="E32" s="30">
+      <c r="D20" s="32">
+        <v>0</v>
+      </c>
+      <c r="E20" s="26">
         <v>315.2</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F20" s="25">
         <v>173.93333435058594</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G20" s="26">
         <v>8914.8166666666675</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H20" s="25">
         <v>311159</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I20" s="26">
         <v>187830.171875</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J20" s="26">
         <v>163.09381666666667</v>
       </c>
-      <c r="K32" s="31">
+      <c r="K20" s="27">
         <f t="shared" si="0"/>
         <v>508556.21569268394</v>
       </c>
-      <c r="L32" s="15"/>
-      <c r="M32" s="16"/>
-      <c r="Q32" s="17"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18" t="s">
+      <c r="L20" s="14"/>
+      <c r="M20" s="15"/>
+      <c r="Q20" s="16"/>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="37">
-        <v>0</v>
-      </c>
-      <c r="E33" s="30">
+      <c r="D21" s="32">
+        <v>0</v>
+      </c>
+      <c r="E21" s="26">
         <v>320.09354838709675</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F21" s="25">
         <v>151.67741394042969</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G21" s="26">
         <v>8422.1612903225814</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H21" s="25">
         <v>303441.6875</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I21" s="26">
         <v>188163.46875</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J21" s="26">
         <v>165.39524193548388</v>
       </c>
-      <c r="K33" s="31">
+      <c r="K21" s="27">
         <f t="shared" si="0"/>
         <v>500664.4837445856</v>
       </c>
-      <c r="L33" s="15"/>
-      <c r="M33" s="16"/>
-      <c r="Q33" s="17"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="15"/>
+      <c r="Q21" s="16"/>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B22" s="17">
+        <v>2023</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="32">
+        <v>0</v>
+      </c>
+      <c r="E22" s="26">
+        <v>254.23870967741934</v>
+      </c>
+      <c r="F22" s="25">
+        <v>167.70967102050781</v>
+      </c>
+      <c r="G22" s="26">
+        <v>8522.9064516129019</v>
+      </c>
+      <c r="H22" s="25">
+        <v>313561.78125</v>
+      </c>
+      <c r="I22" s="26">
+        <v>188007.609375</v>
+      </c>
+      <c r="J22" s="26">
+        <v>136.75872580645162</v>
+      </c>
+      <c r="K22" s="27">
+        <f t="shared" si="0"/>
+        <v>510651.00418311724</v>
+      </c>
+      <c r="L22" s="14"/>
+      <c r="M22" s="15"/>
+      <c r="Q22" s="16"/>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="32">
+        <v>0</v>
+      </c>
+      <c r="E23" s="26">
+        <v>257.67142857142858</v>
+      </c>
+      <c r="F23" s="25">
+        <v>153.14285278320313</v>
+      </c>
+      <c r="G23" s="26">
+        <v>8767.9357142857134</v>
+      </c>
+      <c r="H23" s="25">
+        <v>314904.96875</v>
+      </c>
+      <c r="I23" s="26">
+        <v>184297.609375</v>
+      </c>
+      <c r="J23" s="26">
+        <v>136.52096428571429</v>
+      </c>
+      <c r="K23" s="27">
+        <f t="shared" si="0"/>
+        <v>508517.84908492607</v>
+      </c>
+      <c r="L23" s="14"/>
+      <c r="M23" s="15"/>
+      <c r="Q23" s="16"/>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="32">
+        <v>0</v>
+      </c>
+      <c r="E24" s="26">
+        <v>210.88064516129032</v>
+      </c>
+      <c r="F24" s="25">
+        <v>163.22579956054688</v>
+      </c>
+      <c r="G24" s="26">
+        <v>8588.6419354838708</v>
+      </c>
+      <c r="H24" s="25">
+        <v>313318.1875</v>
+      </c>
+      <c r="I24" s="26">
+        <v>190282.21875</v>
+      </c>
+      <c r="J24" s="26">
+        <v>131.42491935483872</v>
+      </c>
+      <c r="K24" s="27">
+        <f t="shared" si="0"/>
+        <v>512694.57954956056</v>
+      </c>
+      <c r="L24" s="14"/>
+      <c r="M24" s="15"/>
+      <c r="Q24" s="16"/>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="32">
+        <v>0</v>
+      </c>
+      <c r="E25" s="26">
+        <v>91.563333333333333</v>
+      </c>
+      <c r="F25" s="25">
+        <v>176.73333740234375</v>
+      </c>
+      <c r="G25" s="26">
+        <v>9023.3966666666674</v>
+      </c>
+      <c r="H25" s="25">
+        <v>314085.46875</v>
+      </c>
+      <c r="I25" s="26">
+        <v>193214.953125</v>
+      </c>
+      <c r="J25" s="26">
+        <v>148.0009</v>
+      </c>
+      <c r="K25" s="27">
+        <f t="shared" si="0"/>
+        <v>516740.11611240235</v>
+      </c>
+      <c r="L25" s="14"/>
+      <c r="M25" s="15"/>
+      <c r="Q25" s="16"/>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B26" s="17"/>
+      <c r="C26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="32">
+        <v>0</v>
+      </c>
+      <c r="E26" s="26">
+        <v>7.5064516129032253</v>
+      </c>
+      <c r="F26" s="25">
+        <v>179.19354248046875</v>
+      </c>
+      <c r="G26" s="26">
+        <v>8840.1935483870966</v>
+      </c>
+      <c r="H26" s="25">
+        <v>274588.1875</v>
+      </c>
+      <c r="I26" s="26">
+        <v>185487.09375</v>
+      </c>
+      <c r="J26" s="26">
+        <v>139.51614516129032</v>
+      </c>
+      <c r="K26" s="27">
+        <f t="shared" si="0"/>
+        <v>469241.69093764178</v>
+      </c>
+      <c r="L26" s="14"/>
+      <c r="M26" s="15"/>
+      <c r="Q26" s="16"/>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="32">
+        <v>0</v>
+      </c>
+      <c r="E27" s="26">
+        <v>0</v>
+      </c>
+      <c r="F27" s="25">
+        <v>180.86666870117188</v>
+      </c>
+      <c r="G27" s="26">
+        <v>8627.1299999999992</v>
+      </c>
+      <c r="H27" s="25">
+        <v>292851.0625</v>
+      </c>
+      <c r="I27" s="26">
+        <v>180743.5625</v>
+      </c>
+      <c r="J27" s="26">
+        <v>151.38736666666668</v>
+      </c>
+      <c r="K27" s="27">
+        <f t="shared" si="0"/>
+        <v>482554.00903536787</v>
+      </c>
+      <c r="L27" s="14"/>
+      <c r="M27" s="15"/>
+      <c r="Q27" s="16"/>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="32">
+        <v>0</v>
+      </c>
+      <c r="E28" s="26">
+        <v>0</v>
+      </c>
+      <c r="F28" s="25">
+        <v>181.22579956054688</v>
+      </c>
+      <c r="G28" s="26">
+        <v>8897.145161290322</v>
+      </c>
+      <c r="H28" s="25">
+        <v>313778.25</v>
+      </c>
+      <c r="I28" s="26">
+        <v>187091.015625</v>
+      </c>
+      <c r="J28" s="26">
+        <v>138.39966129032257</v>
+      </c>
+      <c r="K28" s="27">
+        <f t="shared" si="0"/>
+        <v>510086.03624714119</v>
+      </c>
+      <c r="L28" s="14"/>
+      <c r="M28" s="15"/>
+      <c r="Q28" s="16"/>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B29" s="17"/>
+      <c r="C29" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="32">
+        <v>0</v>
+      </c>
+      <c r="E29" s="26">
+        <v>0</v>
+      </c>
+      <c r="F29" s="25">
+        <v>186.90322875976563</v>
+      </c>
+      <c r="G29" s="26">
+        <v>8726.1709677419349</v>
+      </c>
+      <c r="H29" s="25">
+        <v>315851.78125</v>
+      </c>
+      <c r="I29" s="26">
+        <v>186857.125</v>
+      </c>
+      <c r="J29" s="26">
+        <v>120.8513870967742</v>
+      </c>
+      <c r="K29" s="27">
+        <f t="shared" si="0"/>
+        <v>511742.83183359849</v>
+      </c>
+      <c r="L29" s="14"/>
+      <c r="M29" s="15"/>
+      <c r="Q29" s="16"/>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="32">
+        <v>0</v>
+      </c>
+      <c r="E30" s="26">
+        <v>0</v>
+      </c>
+      <c r="F30" s="25">
+        <v>186.53334045410156</v>
+      </c>
+      <c r="G30" s="26">
+        <v>8723.5333333333328</v>
+      </c>
+      <c r="H30" s="25">
+        <v>307381.40625</v>
+      </c>
+      <c r="I30" s="26">
+        <v>184120.046875</v>
+      </c>
+      <c r="J30" s="26">
+        <v>123.54013333333334</v>
+      </c>
+      <c r="K30" s="27">
+        <f t="shared" si="0"/>
+        <v>500535.05993212078</v>
+      </c>
+      <c r="L30" s="14"/>
+      <c r="M30" s="15"/>
+      <c r="Q30" s="16"/>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="32">
+        <v>0</v>
+      </c>
+      <c r="E31" s="26"/>
+      <c r="F31" s="25">
+        <v>186</v>
+      </c>
+      <c r="G31" s="26">
+        <v>8826.8096774193546</v>
+      </c>
+      <c r="H31" s="25">
+        <v>308638</v>
+      </c>
+      <c r="I31" s="26">
+        <v>194744.8125</v>
+      </c>
+      <c r="J31" s="26">
+        <v>127.84974193548386</v>
+      </c>
+      <c r="K31" s="27">
+        <f t="shared" si="0"/>
+        <v>512523.47191935487</v>
+      </c>
+      <c r="L31" s="14"/>
+      <c r="M31" s="15"/>
+      <c r="Q31" s="16"/>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="32">
+        <v>0</v>
+      </c>
+      <c r="E32" s="26"/>
+      <c r="F32" s="25">
+        <v>169.43333435058594</v>
+      </c>
+      <c r="G32" s="26">
+        <v>8857.0499999999993</v>
+      </c>
+      <c r="H32" s="25">
+        <v>321725.625</v>
+      </c>
+      <c r="I32" s="26">
+        <v>194110.671875</v>
+      </c>
+      <c r="J32" s="26">
+        <v>138.357</v>
+      </c>
+      <c r="K32" s="27">
+        <f t="shared" si="0"/>
+        <v>525001.13720935059</v>
+      </c>
+      <c r="L32" s="14"/>
+      <c r="M32" s="15"/>
+      <c r="Q32" s="16"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="32">
+        <v>0</v>
+      </c>
+      <c r="E33" s="26"/>
+      <c r="F33" s="25">
+        <v>169.22579956054688</v>
+      </c>
+      <c r="G33" s="26">
+        <v>8849.2032258064537</v>
+      </c>
+      <c r="H33" s="25">
+        <v>323013.6875</v>
+      </c>
+      <c r="I33" s="26">
+        <v>199607.671875</v>
+      </c>
+      <c r="J33" s="26">
+        <v>155.85848387096775</v>
+      </c>
+      <c r="K33" s="27">
+        <f t="shared" si="0"/>
+        <v>531795.646884238</v>
+      </c>
+      <c r="L33" s="14"/>
+      <c r="M33" s="15"/>
+      <c r="Q33" s="16"/>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B34" s="18">
-        <v>2023</v>
-      </c>
-      <c r="C34" s="18" t="s">
+      <c r="B34" s="17">
+        <v>2024</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="37">
-        <v>0</v>
-      </c>
-      <c r="E34" s="30">
-        <v>254.23870967741934</v>
-      </c>
-      <c r="F34" s="28">
-        <v>167.70967102050781</v>
-      </c>
-      <c r="G34" s="30">
-        <v>8509.3387096774186</v>
-      </c>
-      <c r="H34" s="28">
-        <v>313543.96875</v>
-      </c>
-      <c r="I34" s="30">
-        <v>188007.609375</v>
-      </c>
-      <c r="J34" s="30">
-        <v>136.75872580645162</v>
-      </c>
-      <c r="K34" s="31">
+      <c r="D34" s="32"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="25">
+        <v>148.45161437988281</v>
+      </c>
+      <c r="G34" s="26">
+        <v>8166.7838709677417</v>
+      </c>
+      <c r="H34" s="25">
+        <v>305088.90625</v>
+      </c>
+      <c r="I34" s="26">
+        <v>198348.90625</v>
+      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="27">
         <f t="shared" si="0"/>
-        <v>510619.62394118175</v>
-      </c>
-      <c r="L34" s="15"/>
-      <c r="M34" s="16"/>
-      <c r="Q34" s="17"/>
+        <v>511753.04798534763</v>
+      </c>
+      <c r="L34" s="14"/>
+      <c r="M34" s="15"/>
+      <c r="Q34" s="16"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B35" s="18"/>
-      <c r="C35" s="18" t="s">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="37">
-        <v>0</v>
-      </c>
-      <c r="E35" s="30">
-        <v>257.67142857142858</v>
-      </c>
-      <c r="F35" s="28">
-        <v>153.14285278320313</v>
-      </c>
-      <c r="G35" s="30">
-        <v>8766.4642857142862</v>
-      </c>
-      <c r="H35" s="28">
-        <v>314895.71875</v>
-      </c>
-      <c r="I35" s="30">
-        <v>184297.609375</v>
-      </c>
-      <c r="J35" s="30">
-        <v>136.52096428571429</v>
-      </c>
-      <c r="K35" s="31">
-        <f t="shared" si="0"/>
-        <v>508507.12765635463</v>
-      </c>
-      <c r="L35" s="15"/>
-      <c r="M35" s="16"/>
-      <c r="Q35" s="17"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="25">
+        <v>156.51724243164063</v>
+      </c>
+      <c r="G35" s="26">
+        <v>8776.9000000000015</v>
+      </c>
+      <c r="H35" s="25">
+        <v>315623.125</v>
+      </c>
+      <c r="I35" s="26">
+        <v>202990.390625</v>
+      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="27"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="15"/>
+      <c r="Q35" s="16"/>
     </row>
     <row r="36" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B36" s="18"/>
-      <c r="C36" s="18" t="s">
+      <c r="B36" s="17"/>
+      <c r="C36" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="37">
-        <v>0</v>
-      </c>
-      <c r="E36" s="30">
-        <v>210.88064516129032</v>
-      </c>
-      <c r="F36" s="28">
-        <v>163.22579956054688</v>
-      </c>
-      <c r="G36" s="30">
-        <v>8611.0806451612898</v>
-      </c>
-      <c r="H36" s="28">
-        <v>313283.90625</v>
-      </c>
-      <c r="I36" s="30">
-        <v>190282.21875</v>
-      </c>
-      <c r="J36" s="30">
-        <v>131.42491935483872</v>
-      </c>
-      <c r="K36" s="31">
-        <f t="shared" si="0"/>
-        <v>512682.73700923799</v>
-      </c>
-      <c r="L36" s="15"/>
-      <c r="M36" s="16"/>
-      <c r="Q36" s="17"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="25">
+        <v>163.41935729980469</v>
+      </c>
+      <c r="G36" s="26"/>
+      <c r="H36" s="25">
+        <v>314769.625</v>
+      </c>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="27"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="15"/>
+      <c r="Q36" s="16"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B37" s="18"/>
-      <c r="C37" s="18" t="s">
+      <c r="B37" s="17"/>
+      <c r="C37" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="37">
-        <v>0</v>
-      </c>
-      <c r="E37" s="30">
-        <v>91.563333333333333</v>
-      </c>
-      <c r="F37" s="28">
-        <v>176.73333740234375</v>
-      </c>
-      <c r="G37" s="30">
-        <v>9051.4800000000014</v>
-      </c>
-      <c r="H37" s="28">
-        <v>314054.625</v>
-      </c>
-      <c r="I37" s="30">
-        <v>193214.953125</v>
-      </c>
-      <c r="J37" s="30">
-        <v>148.0009</v>
-      </c>
-      <c r="K37" s="31">
-        <f t="shared" si="0"/>
-        <v>516737.35569573566</v>
-      </c>
-      <c r="L37" s="15"/>
-      <c r="M37" s="16"/>
-      <c r="Q37" s="17"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="25">
+        <v>315406.8125</v>
+      </c>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="27"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="15"/>
+      <c r="Q37" s="16"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B38" s="18"/>
-      <c r="C38" s="18" t="s">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="37">
-        <v>0</v>
-      </c>
-      <c r="E38" s="30">
-        <v>7.5064516129032253</v>
-      </c>
-      <c r="F38" s="28">
-        <v>179.19354248046875</v>
-      </c>
-      <c r="G38" s="30">
-        <v>8867.1064516129027</v>
-      </c>
-      <c r="H38" s="28">
-        <v>274496.875</v>
-      </c>
-      <c r="I38" s="30">
-        <v>185487.09375</v>
-      </c>
-      <c r="J38" s="30">
-        <v>139.51614516129032</v>
-      </c>
-      <c r="K38" s="31">
-        <f t="shared" si="0"/>
-        <v>469177.29134086758</v>
-      </c>
-      <c r="L38" s="15"/>
-      <c r="M38" s="16"/>
-      <c r="Q38" s="17"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="27"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="15"/>
+      <c r="Q38" s="16"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B39" s="18"/>
-      <c r="C39" s="18" t="s">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="37">
-        <v>0</v>
-      </c>
-      <c r="E39" s="30">
-        <v>0</v>
-      </c>
-      <c r="F39" s="28">
-        <v>180.86666870117188</v>
-      </c>
-      <c r="G39" s="30">
-        <v>8651.3933333333334</v>
-      </c>
-      <c r="H39" s="28">
-        <v>292812.28125</v>
-      </c>
-      <c r="I39" s="30">
-        <v>180743.5625</v>
-      </c>
-      <c r="J39" s="30">
-        <v>151.38736666666668</v>
-      </c>
-      <c r="K39" s="31">
-        <f t="shared" si="0"/>
-        <v>482539.49111870117</v>
-      </c>
-      <c r="L39" s="15"/>
-      <c r="M39" s="16"/>
-      <c r="Q39" s="17"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="15"/>
+      <c r="Q39" s="16"/>
     </row>
     <row r="40" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B40" s="18"/>
-      <c r="C40" s="18" t="s">
+      <c r="B40" s="17"/>
+      <c r="C40" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="37">
-        <v>0</v>
-      </c>
-      <c r="E40" s="30">
-        <v>0</v>
-      </c>
-      <c r="F40" s="28">
-        <v>181.22579956054688</v>
-      </c>
-      <c r="G40" s="30">
-        <v>8930.8645161290315</v>
-      </c>
-      <c r="H40" s="28">
-        <v>313557.8125</v>
-      </c>
-      <c r="I40" s="30">
-        <v>187091.015625</v>
-      </c>
-      <c r="J40" s="30">
-        <v>138.39966129032257</v>
-      </c>
-      <c r="K40" s="31">
-        <f t="shared" si="0"/>
-        <v>509899.31810197991</v>
-      </c>
-      <c r="L40" s="15"/>
-      <c r="M40" s="16"/>
-      <c r="Q40" s="17"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="27"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="15"/>
+      <c r="Q40" s="16"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B41" s="18"/>
-      <c r="C41" s="20" t="s">
+      <c r="B41" s="17"/>
+      <c r="C41" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="37"/>
-      <c r="E41" s="30">
-        <v>0</v>
-      </c>
-      <c r="F41" s="28">
-        <v>186.90322875976563</v>
-      </c>
-      <c r="G41" s="30">
-        <v>8763.351612903225</v>
-      </c>
-      <c r="H41" s="28">
-        <v>314809.84375</v>
-      </c>
-      <c r="I41" s="30">
-        <v>186857.125</v>
-      </c>
-      <c r="J41" s="30"/>
-      <c r="K41" s="31">
-        <f t="shared" si="0"/>
-        <v>510617.223591663</v>
-      </c>
-      <c r="L41" s="15"/>
-      <c r="M41" s="16"/>
-      <c r="Q41" s="17"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="15"/>
+      <c r="Q41" s="16"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B42" s="18"/>
-      <c r="C42" s="18" t="s">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="37"/>
-      <c r="E42" s="30">
-        <v>0</v>
-      </c>
-      <c r="F42" s="28">
-        <v>186.53334045410156</v>
-      </c>
-      <c r="G42" s="30">
-        <v>8763.66</v>
-      </c>
-      <c r="H42" s="28">
-        <v>306052.34375</v>
-      </c>
-      <c r="I42" s="30">
-        <v>184120.046875</v>
-      </c>
-      <c r="J42" s="30"/>
-      <c r="K42" s="31">
-        <f t="shared" si="0"/>
-        <v>499122.58396545408</v>
-      </c>
-      <c r="L42" s="15"/>
-      <c r="M42" s="16"/>
-      <c r="Q42" s="17"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="27"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="15"/>
+      <c r="Q42" s="16"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B43" s="18"/>
-      <c r="C43" s="18" t="s">
+      <c r="B43" s="17"/>
+      <c r="C43" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="37"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="28">
-        <v>307754.25</v>
-      </c>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="16"/>
-      <c r="Q43" s="17"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="15"/>
+      <c r="Q43" s="16"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B44" s="18"/>
-      <c r="C44" s="18" t="s">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="37"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="16"/>
-      <c r="Q44" s="17"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="27"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="15"/>
+      <c r="Q44" s="16"/>
     </row>
     <row r="45" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="21"/>
-      <c r="C45" s="21" t="s">
+      <c r="B45" s="20"/>
+      <c r="C45" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="38"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="16"/>
-      <c r="Q45" s="17"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="15"/>
+      <c r="Q45" s="16"/>
     </row>
     <row r="46" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C46" s="23"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="59" t="s">
+      <c r="C46" s="22"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="K46" s="60">
-        <v>45295</v>
+      <c r="K46" s="54">
+        <v>45448</v>
       </c>
     </row>
   </sheetData>
@@ -4737,7 +4576,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="11"/>
@@ -4748,8 +4587,8 @@
     <col min="14" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="91.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="91.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>16</v>
       </c>
@@ -4760,7 +4599,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:17" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>20</v>
       </c>
@@ -4771,7 +4610,7 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
@@ -4780,1200 +4619,1032 @@
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="61" t="s">
+    <row r="5" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="62"/>
-      <c r="K5" s="63"/>
-    </row>
-    <row r="6" spans="1:17" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="64"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="66"/>
-    </row>
-    <row r="7" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="67" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="69" t="s">
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="57"/>
+    </row>
+    <row r="6" spans="1:11" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="58"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="60"/>
+    </row>
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="E7" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="F7" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="I7" s="71" t="s">
+      <c r="I7" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="69" t="s">
+      <c r="J7" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="K7" s="73" t="s">
+      <c r="K7" s="70" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="70"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="74"/>
-    </row>
-    <row r="9" spans="1:17" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="70"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="70"/>
-      <c r="K9" s="74"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B10" s="14">
-        <v>2021</v>
-      </c>
-      <c r="C10" s="14" t="s">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="71"/>
+    </row>
+    <row r="9" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
+      <c r="G9" s="66"/>
+      <c r="H9" s="66"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="66"/>
+      <c r="K9" s="72"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="17">
+        <v>2022</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="36">
-        <v>0</v>
-      </c>
-      <c r="E10" s="27">
-        <v>12.12145165483871</v>
-      </c>
-      <c r="F10" s="26">
-        <v>6.5969953247192388</v>
-      </c>
-      <c r="G10" s="27">
-        <v>318.36465045999995</v>
-      </c>
-      <c r="H10" s="26">
-        <v>9888.4455603250008</v>
-      </c>
-      <c r="I10" s="27">
-        <v>5547.3001365937498</v>
-      </c>
-      <c r="J10" s="27">
-        <v>5.9924644143903212</v>
-      </c>
-      <c r="K10" s="29">
-        <f t="shared" ref="K10:K36" si="0">SUM(D10:J10)</f>
-        <v>15778.821258772699</v>
-      </c>
-      <c r="L10" s="15"/>
-      <c r="M10" s="16"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="17"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B11" s="18"/>
-      <c r="C11" s="18" t="s">
+      <c r="D10" s="37">
+        <v>0</v>
+      </c>
+      <c r="E10" s="26">
+        <v>10.157732058709678</v>
+      </c>
+      <c r="F10" s="25">
+        <v>5.6321091270599357</v>
+      </c>
+      <c r="G10" s="26">
+        <v>301.36875874258067</v>
+      </c>
+      <c r="H10" s="25">
+        <v>10223.519313774999</v>
+      </c>
+      <c r="I10" s="26">
+        <v>6021.9007710624992</v>
+      </c>
+      <c r="J10" s="26">
+        <v>6.48561001977742</v>
+      </c>
+      <c r="K10" s="27">
+        <f t="shared" ref="K10:K24" si="0">SUM(D10:J10)</f>
+        <v>16569.064294785625</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B11" s="17"/>
+      <c r="C11" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D11" s="37">
         <v>0</v>
       </c>
-      <c r="E11" s="30">
-        <v>11.415192202857142</v>
-      </c>
-      <c r="F11" s="28">
-        <v>6.6202260333465572</v>
-      </c>
-      <c r="G11" s="30">
-        <v>297.56422493642856</v>
-      </c>
-      <c r="H11" s="28">
-        <v>9583.3825953875003</v>
-      </c>
-      <c r="I11" s="30">
-        <v>5572.7062323406244</v>
-      </c>
-      <c r="J11" s="30">
-        <v>5.6882323495071425</v>
-      </c>
-      <c r="K11" s="31">
-        <f t="shared" si="0"/>
-        <v>15477.376703250264</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="16"/>
-      <c r="Q11" s="17"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="37">
-        <v>0</v>
-      </c>
-      <c r="E12" s="30">
-        <v>10.52637091548387</v>
-      </c>
-      <c r="F12" s="28">
-        <v>6.4944689623596181</v>
-      </c>
-      <c r="G12" s="30">
-        <v>320.53365040838713</v>
-      </c>
-      <c r="H12" s="28">
-        <v>10095.520442493749</v>
-      </c>
-      <c r="I12" s="30">
-        <v>5586.0325277249995</v>
-      </c>
-      <c r="J12" s="30">
-        <v>6.0302937556645171</v>
-      </c>
-      <c r="K12" s="31">
-        <f t="shared" si="0"/>
-        <v>16025.137754260644</v>
-      </c>
-      <c r="L12" s="15"/>
-      <c r="M12" s="16"/>
-      <c r="Q12" s="17"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="37">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30">
-        <v>8.690805344666666</v>
-      </c>
-      <c r="F13" s="28">
-        <v>6.9381414951995843</v>
-      </c>
-      <c r="G13" s="30">
-        <v>332.26883248733333</v>
-      </c>
-      <c r="H13" s="28">
-        <v>10149.910444399999</v>
-      </c>
-      <c r="I13" s="30">
-        <v>5698.9432361562494</v>
-      </c>
-      <c r="J13" s="30">
-        <v>6.6858995646699997</v>
-      </c>
-      <c r="K13" s="31">
-        <f t="shared" si="0"/>
-        <v>16203.437359448117</v>
-      </c>
-      <c r="L13" s="15"/>
-      <c r="M13" s="16"/>
-      <c r="Q13" s="17"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="37">
-        <v>0</v>
-      </c>
-      <c r="E14" s="30">
-        <v>1.1391806451612903E-4</v>
-      </c>
-      <c r="F14" s="28">
-        <v>6.8738158564605705</v>
-      </c>
-      <c r="G14" s="30">
-        <v>325.05528622516124</v>
-      </c>
-      <c r="H14" s="28">
-        <v>9968.0115612874997</v>
-      </c>
-      <c r="I14" s="30">
-        <v>5548.3005329968755</v>
-      </c>
-      <c r="J14" s="30">
-        <v>6.7676375416903216</v>
-      </c>
-      <c r="K14" s="31">
-        <f t="shared" si="0"/>
-        <v>15855.008947825752</v>
-      </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="16"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B15" s="18"/>
-      <c r="C15" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="37">
-        <v>0</v>
-      </c>
-      <c r="E15" s="30">
-        <v>7.651496666666667E-3</v>
-      </c>
-      <c r="F15" s="28">
-        <v>7.2418472707427979</v>
-      </c>
-      <c r="G15" s="30">
-        <v>309.4002746806666</v>
-      </c>
-      <c r="H15" s="28">
-        <v>9867.4488234625005</v>
-      </c>
-      <c r="I15" s="30">
-        <v>5547.9181420937493</v>
-      </c>
-      <c r="J15" s="30">
-        <v>5.8958554593099999</v>
-      </c>
-      <c r="K15" s="31">
-        <f t="shared" si="0"/>
-        <v>15737.912594463636</v>
-      </c>
-      <c r="L15" s="15"/>
-      <c r="M15" s="16"/>
-      <c r="Q15" s="17"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="37">
-        <v>0</v>
-      </c>
-      <c r="E16" s="30">
-        <v>2.2783612903225807E-3</v>
-      </c>
-      <c r="F16" s="28">
-        <v>7.5174532164794918</v>
-      </c>
-      <c r="G16" s="30">
-        <v>317.11804508</v>
-      </c>
-      <c r="H16" s="28">
-        <v>10077.696501724999</v>
-      </c>
-      <c r="I16" s="30">
-        <v>5616.4108087937502</v>
-      </c>
-      <c r="J16" s="30">
-        <v>1.7527336576096775</v>
-      </c>
-      <c r="K16" s="31">
-        <f t="shared" si="0"/>
-        <v>16020.497820834127</v>
-      </c>
-      <c r="L16" s="15"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q16" s="17"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B17" s="20"/>
-      <c r="C17" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="37">
-        <v>0</v>
-      </c>
-      <c r="E17" s="30">
-        <v>7.5185922580645152E-3</v>
-      </c>
-      <c r="F17" s="28">
-        <v>5.9351310917602538</v>
-      </c>
-      <c r="G17" s="30">
-        <v>315.34297379870969</v>
-      </c>
-      <c r="H17" s="28">
-        <v>10214.095833481249</v>
-      </c>
-      <c r="I17" s="30">
-        <v>5815.5415613343748</v>
-      </c>
-      <c r="J17" s="30">
-        <v>1.0811616053129032</v>
-      </c>
-      <c r="K17" s="31">
-        <f t="shared" si="0"/>
-        <v>16352.004179903664</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="16"/>
-      <c r="Q17" s="17"/>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="18"/>
-      <c r="C18" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="37">
-        <v>0</v>
-      </c>
-      <c r="E18" s="30">
-        <v>5.6267929333333327E-2</v>
-      </c>
-      <c r="F18" s="35">
-        <v>5.4808258122283933</v>
-      </c>
-      <c r="G18" s="30">
-        <v>320.65280110933338</v>
-      </c>
-      <c r="H18" s="28">
-        <v>10022.568203962499</v>
-      </c>
-      <c r="I18" s="30">
-        <v>5917.7673961031251</v>
-      </c>
-      <c r="J18" s="30">
-        <v>6.7215308189166674</v>
-      </c>
-      <c r="K18" s="31">
-        <f t="shared" si="0"/>
-        <v>16273.247025735436</v>
-      </c>
-      <c r="L18" s="15"/>
-      <c r="M18" s="16"/>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B19" s="18"/>
-      <c r="C19" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" s="37">
-        <v>0</v>
-      </c>
-      <c r="E19" s="30">
-        <v>2.4606301935483871E-2</v>
-      </c>
-      <c r="F19" s="35">
-        <v>6.7690112023406988</v>
-      </c>
-      <c r="G19" s="30">
-        <v>322.23513062000001</v>
-      </c>
-      <c r="H19" s="28">
-        <v>10249.530723837499</v>
-      </c>
-      <c r="I19" s="30">
-        <v>5703.4690228624995</v>
-      </c>
-      <c r="J19" s="30">
-        <v>6.1265602160838712</v>
-      </c>
-      <c r="K19" s="31">
-        <f t="shared" si="0"/>
-        <v>16288.155055040357</v>
-      </c>
-      <c r="L19" s="15"/>
-      <c r="M19" s="16"/>
-      <c r="Q19" s="17"/>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B20" s="18"/>
-      <c r="C20" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="37">
-        <v>0</v>
-      </c>
-      <c r="E20" s="30">
-        <v>8.7965137139999996</v>
-      </c>
-      <c r="F20" s="28">
-        <v>6.7168368122283937</v>
-      </c>
-      <c r="G20" s="30">
-        <v>322.27821443200003</v>
-      </c>
-      <c r="H20" s="28">
-        <v>10430.48163065625</v>
-      </c>
-      <c r="I20" s="30">
-        <v>6073.4942980812493</v>
-      </c>
-      <c r="J20" s="30">
-        <v>6.6331319007733329</v>
-      </c>
-      <c r="K20" s="31">
-        <f t="shared" si="0"/>
-        <v>16848.4006255965</v>
-      </c>
-      <c r="L20" s="15"/>
-      <c r="M20" s="16"/>
-      <c r="Q20" s="17"/>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B21" s="42"/>
-      <c r="C21" s="42" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="43">
-        <v>0</v>
-      </c>
-      <c r="E21" s="30">
-        <v>11.714422410322582</v>
-      </c>
-      <c r="F21" s="30">
-        <v>6.6072476376403806</v>
-      </c>
-      <c r="G21" s="30">
-        <v>308.83005021419353</v>
-      </c>
-      <c r="H21" s="30">
-        <v>10125.0953164125</v>
-      </c>
-      <c r="I21" s="30">
-        <v>6031.3214924031245</v>
-      </c>
-      <c r="J21" s="30">
-        <v>6.8458958344709666</v>
-      </c>
-      <c r="K21" s="31">
-        <f t="shared" si="0"/>
-        <v>16490.414424912251</v>
-      </c>
-      <c r="L21" s="22"/>
-      <c r="M21" s="16"/>
-      <c r="Q21" s="17"/>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B22" s="18">
-        <v>2022</v>
-      </c>
-      <c r="C22" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="43">
-        <v>0</v>
-      </c>
-      <c r="E22" s="30">
-        <v>10.157732058709678</v>
-      </c>
-      <c r="F22" s="28">
-        <v>5.6321091270599357</v>
-      </c>
-      <c r="G22" s="30">
-        <v>301.36875874258067</v>
-      </c>
-      <c r="H22" s="28">
-        <v>10223.519313774999</v>
-      </c>
-      <c r="I22" s="30">
-        <v>6021.9007710624992</v>
-      </c>
-      <c r="J22" s="30">
-        <v>6.48561001977742</v>
-      </c>
-      <c r="K22" s="31">
-        <f t="shared" si="0"/>
-        <v>16569.064294785625</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B23" s="18"/>
-      <c r="C23" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="43">
-        <v>0</v>
-      </c>
-      <c r="E23" s="30">
+      <c r="E11" s="26">
         <v>9.7965222871428566</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F11" s="25">
         <v>5.6667318333465575</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G11" s="26">
         <v>301.52336996714286</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H11" s="25">
         <v>10484.32756700625</v>
       </c>
-      <c r="I23" s="30">
+      <c r="I11" s="26">
         <v>6118.1363668062495</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J11" s="26">
         <v>6.266268659103571</v>
       </c>
-      <c r="K23" s="31">
+      <c r="K11" s="27">
         <f t="shared" si="0"/>
         <v>16925.716826559237</v>
       </c>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B24" s="18"/>
-      <c r="C24" s="18" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="43">
-        <v>0</v>
-      </c>
-      <c r="E24" s="30">
+      <c r="D12" s="37">
+        <v>0</v>
+      </c>
+      <c r="E12" s="26">
         <v>8.3660287399999991</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F12" s="25">
         <v>5.7676717976593013</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G12" s="26">
         <v>313.49977951483868</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H12" s="25">
         <v>10703.7250374125</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I12" s="26">
         <v>6131.728625271875</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J12" s="26">
         <v>5.945010705435485</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K12" s="27">
         <f t="shared" si="0"/>
         <v>17169.032153442309</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B25" s="18"/>
-      <c r="C25" s="18" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="37">
-        <v>0</v>
-      </c>
-      <c r="E25" s="30">
+      <c r="D13" s="32">
+        <v>0</v>
+      </c>
+      <c r="E13" s="26">
         <v>4.3666502899999999</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F13" s="25">
         <v>6.227140953713989</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G13" s="26">
         <v>307.52883631133335</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H13" s="25">
         <v>10963.276311600001</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I13" s="26">
         <v>6242.8432552187505</v>
       </c>
-      <c r="J25" s="30">
+      <c r="J13" s="26">
         <v>5.9942354605666663</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K13" s="27">
         <f t="shared" si="0"/>
         <v>17530.236429834364</v>
       </c>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B26" s="18"/>
-      <c r="C26" s="18" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B14" s="17"/>
+      <c r="C14" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="37">
-        <v>0</v>
-      </c>
-      <c r="E26" s="30">
+      <c r="D14" s="32">
+        <v>0</v>
+      </c>
+      <c r="E14" s="26">
         <v>1.6973791612903227E-2</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F14" s="25">
         <v>6.6528150894195557</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G14" s="26">
         <v>313.29244863741934</v>
       </c>
-      <c r="H26" s="28">
+      <c r="H14" s="25">
         <v>10665.408696412498</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I14" s="26">
         <v>6171.0398447687503</v>
       </c>
-      <c r="J26" s="30">
+      <c r="J14" s="26">
         <v>6.6779914295903229</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K14" s="27">
         <f t="shared" si="0"/>
         <v>17163.088770129292</v>
       </c>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B27" s="18"/>
-      <c r="C27" s="18" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="37">
-        <v>0</v>
-      </c>
-      <c r="E27" s="30">
+      <c r="D15" s="32">
+        <v>0</v>
+      </c>
+      <c r="E15" s="26">
         <v>1.4714416666666667E-2</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F15" s="25">
         <v>6.9864048537139887</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G15" s="26">
         <v>306.48270014399998</v>
       </c>
-      <c r="H27" s="28">
+      <c r="H15" s="25">
         <v>10532.7979590875</v>
       </c>
-      <c r="I27" s="30">
+      <c r="I15" s="26">
         <v>6112.9506385125005</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J15" s="26">
         <v>6.1818207300000001</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K15" s="27">
         <f t="shared" si="0"/>
         <v>16965.414237744382</v>
       </c>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B28" s="18"/>
-      <c r="C28" s="18" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="37">
-        <v>0</v>
-      </c>
-      <c r="E28" s="30">
+      <c r="D16" s="32">
+        <v>0</v>
+      </c>
+      <c r="E16" s="26">
         <v>1.3442331612903227E-2</v>
       </c>
-      <c r="F28" s="28">
+      <c r="F16" s="25">
         <v>6.9284964752807614</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G16" s="26">
         <v>304.48817710322584</v>
       </c>
-      <c r="H28" s="28">
+      <c r="H16" s="25">
         <v>10917.300013143751</v>
       </c>
-      <c r="I28" s="30">
+      <c r="I16" s="26">
         <v>6258.8672549687499</v>
       </c>
-      <c r="J28" s="30">
+      <c r="J16" s="26">
         <v>5.6942702103516121</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K16" s="27">
         <f t="shared" si="0"/>
         <v>17493.291654232973</v>
       </c>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B29" s="20"/>
-      <c r="C29" s="20" t="s">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B17" s="19"/>
+      <c r="C17" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="37">
-        <v>0</v>
-      </c>
-      <c r="E29" s="30">
+      <c r="D17" s="32">
+        <v>0</v>
+      </c>
+      <c r="E17" s="26">
         <v>1.4239758064516128E-2</v>
       </c>
-      <c r="F29" s="28">
+      <c r="F17" s="25">
         <v>7.0674765835205084</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G17" s="26">
         <v>305.81053799612897</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H17" s="25">
         <v>10783.0946009125</v>
       </c>
-      <c r="I29" s="30">
+      <c r="I17" s="26">
         <v>5983.0811970124996</v>
       </c>
-      <c r="J29" s="30">
+      <c r="J17" s="26">
         <v>5.5336821931645161</v>
       </c>
-      <c r="K29" s="31">
+      <c r="K17" s="27">
         <f t="shared" si="0"/>
         <v>17084.601734455879</v>
       </c>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B30" s="18"/>
-      <c r="C30" s="18" t="s">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="37">
-        <v>0</v>
-      </c>
-      <c r="E30" s="30">
-        <v>0</v>
-      </c>
-      <c r="F30" s="35">
+      <c r="D18" s="32">
+        <v>0</v>
+      </c>
+      <c r="E18" s="26">
+        <v>0</v>
+      </c>
+      <c r="F18" s="31">
         <v>7.0688059462860107</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G18" s="26">
         <v>311.10844188266663</v>
       </c>
-      <c r="H30" s="28">
+      <c r="H18" s="25">
         <v>10869.405690475</v>
       </c>
-      <c r="I30" s="30">
+      <c r="I18" s="26">
         <v>6186.5446095406251</v>
       </c>
-      <c r="J30" s="30">
+      <c r="J18" s="26">
         <v>4.8346611465366669</v>
       </c>
-      <c r="K30" s="31">
+      <c r="K18" s="27">
         <f t="shared" si="0"/>
         <v>17378.962208991114</v>
       </c>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B31" s="18"/>
-      <c r="C31" s="18" t="s">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="37">
-        <v>0</v>
-      </c>
-      <c r="E31" s="30">
+      <c r="D19" s="32">
+        <v>0</v>
+      </c>
+      <c r="E19" s="26">
         <v>0.58394399870967739</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F19" s="31">
         <v>6.5070001058990474</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G19" s="26">
         <v>319.96531318451605</v>
       </c>
-      <c r="H31" s="28">
+      <c r="H19" s="25">
         <v>10934.081069631249</v>
       </c>
-      <c r="I31" s="30">
+      <c r="I19" s="26">
         <v>6493.0494033812502</v>
       </c>
-      <c r="J31" s="30">
+      <c r="J19" s="26">
         <v>5.6928564871709684</v>
       </c>
-      <c r="K31" s="31">
+      <c r="K19" s="27">
         <f t="shared" si="0"/>
         <v>17759.879586788797</v>
       </c>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B32" s="18"/>
-      <c r="C32" s="18" t="s">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="37">
-        <v>0</v>
-      </c>
-      <c r="E32" s="30">
+      <c r="D20" s="32">
+        <v>0</v>
+      </c>
+      <c r="E20" s="26">
         <v>11.131161919999998</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F20" s="25">
         <v>6.1423861292572024</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G20" s="26">
         <v>314.82318465666668</v>
       </c>
-      <c r="H32" s="28">
+      <c r="H20" s="25">
         <v>10988.455621399999</v>
       </c>
-      <c r="I32" s="30">
+      <c r="I20" s="26">
         <v>6633.1473876968748</v>
       </c>
-      <c r="J32" s="30">
+      <c r="J20" s="26">
         <v>5.7595928980566669</v>
       </c>
-      <c r="K32" s="31">
+      <c r="K20" s="27">
         <f t="shared" si="0"/>
         <v>17959.459334700852</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="37">
-        <v>0</v>
-      </c>
-      <c r="E33" s="30">
+      <c r="D21" s="32">
+        <v>0</v>
+      </c>
+      <c r="E21" s="26">
         <v>11.303975623870967</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F21" s="25">
         <v>5.356427202340698</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G21" s="26">
         <v>297.42525710322582</v>
       </c>
-      <c r="H33" s="28">
+      <c r="H21" s="25">
         <v>10715.9218173875</v>
       </c>
-      <c r="I33" s="30">
+      <c r="I21" s="26">
         <v>6644.9176335187494</v>
       </c>
-      <c r="J33" s="30">
+      <c r="J21" s="26">
         <v>5.8408668108548385</v>
       </c>
-      <c r="K33" s="31">
+      <c r="K21" s="27">
         <f t="shared" si="0"/>
         <v>17680.765977646537</v>
       </c>
     </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B22" s="17">
+        <v>2023</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="32">
+        <v>0</v>
+      </c>
+      <c r="E22" s="26">
+        <v>8.9783383367741934</v>
+      </c>
+      <c r="F22" s="25">
+        <v>5.9225999482208254</v>
+      </c>
+      <c r="G22" s="26">
+        <v>300.98303217612897</v>
+      </c>
+      <c r="H22" s="25">
+        <v>11073.30888013125</v>
+      </c>
+      <c r="I22" s="26">
+        <v>6639.4135220343742</v>
+      </c>
+      <c r="J22" s="26">
+        <v>4.8295796983645163</v>
+      </c>
+      <c r="K22" s="27">
+        <f t="shared" si="0"/>
+        <v>18033.435952325111</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="32">
+        <v>0</v>
+      </c>
+      <c r="E23" s="26">
+        <v>9.0995634314285709</v>
+      </c>
+      <c r="F23" s="25">
+        <v>5.4081785888977052</v>
+      </c>
+      <c r="G23" s="26">
+        <v>309.63614257571425</v>
+      </c>
+      <c r="H23" s="25">
+        <v>11120.743009418751</v>
+      </c>
+      <c r="I23" s="26">
+        <v>6508.3963560343755</v>
+      </c>
+      <c r="J23" s="26">
+        <v>4.8211832453642858</v>
+      </c>
+      <c r="K23" s="27">
+        <f t="shared" si="0"/>
+        <v>17958.104433294531</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="32">
+        <v>0</v>
+      </c>
+      <c r="E24" s="26">
+        <v>7.4471656316129025</v>
+      </c>
+      <c r="F24" s="25">
+        <v>5.7642538211608878</v>
+      </c>
+      <c r="G24" s="26">
+        <v>303.30445449483869</v>
+      </c>
+      <c r="H24" s="25">
+        <v>11064.706464287501</v>
+      </c>
+      <c r="I24" s="26">
+        <v>6719.7404422687496</v>
+      </c>
+      <c r="J24" s="26">
+        <v>4.641218457048387</v>
+      </c>
+      <c r="K24" s="27">
+        <f t="shared" si="0"/>
+        <v>18105.603998960909</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="32">
+        <v>0</v>
+      </c>
+      <c r="E25" s="26">
+        <v>3.2335224913333329</v>
+      </c>
+      <c r="F25" s="25">
+        <v>6.2412671170288085</v>
+      </c>
+      <c r="G25" s="26">
+        <v>318.65764392466667</v>
+      </c>
+      <c r="H25" s="25">
+        <v>11091.80269471875</v>
+      </c>
+      <c r="I25" s="26">
+        <v>6823.3087836281247</v>
+      </c>
+      <c r="J25" s="26">
+        <v>5.2265925831399995</v>
+      </c>
+      <c r="K25" s="27">
+        <f t="shared" ref="K25:K34" si="1">SUM(D25:J25)</f>
+        <v>18248.470504463043</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B26" s="17"/>
+      <c r="C26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="32">
+        <v>0</v>
+      </c>
+      <c r="E26" s="26">
+        <v>0.26508733612903224</v>
+      </c>
+      <c r="F26" s="25">
+        <v>6.3281482752807614</v>
+      </c>
+      <c r="G26" s="26">
+        <v>312.18789908387095</v>
+      </c>
+      <c r="H26" s="25">
+        <v>9696.9720062875003</v>
+      </c>
+      <c r="I26" s="26">
+        <v>6550.4025209437505</v>
+      </c>
+      <c r="J26" s="26">
+        <v>4.9269568599129032</v>
+      </c>
+      <c r="K26" s="27">
+        <f t="shared" si="1"/>
+        <v>16571.082618786444</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B27" s="17"/>
+      <c r="C27" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="32">
+        <v>0</v>
+      </c>
+      <c r="E27" s="26">
+        <v>0</v>
+      </c>
+      <c r="F27" s="25">
+        <v>6.3872340585144043</v>
+      </c>
+      <c r="G27" s="26">
+        <v>304.66364509799996</v>
+      </c>
+      <c r="H27" s="25">
+        <v>10341.918131762501</v>
+      </c>
+      <c r="I27" s="26">
+        <v>6382.8866122624995</v>
+      </c>
+      <c r="J27" s="26">
+        <v>5.3461842988866675</v>
+      </c>
+      <c r="K27" s="27">
+        <f t="shared" si="1"/>
+        <v>17041.201807480404</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="32">
+        <v>0</v>
+      </c>
+      <c r="E28" s="26">
+        <v>0</v>
+      </c>
+      <c r="F28" s="25">
+        <v>6.3999166211608882</v>
+      </c>
+      <c r="G28" s="26">
+        <v>314.19912251290316</v>
+      </c>
+      <c r="H28" s="25">
+        <v>11080.953387449999</v>
+      </c>
+      <c r="I28" s="26">
+        <v>6607.0443803906255</v>
+      </c>
+      <c r="J28" s="26">
+        <v>4.8875286786032257</v>
+      </c>
+      <c r="K28" s="27">
+        <f t="shared" si="1"/>
+        <v>18013.484335653291</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B29" s="17"/>
+      <c r="C29" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="32">
+        <v>0</v>
+      </c>
+      <c r="E29" s="26">
+        <v>0</v>
+      </c>
+      <c r="F29" s="25">
+        <v>6.6004127623596185</v>
+      </c>
+      <c r="G29" s="26">
+        <v>308.16123725741932</v>
+      </c>
+      <c r="H29" s="25">
+        <v>11154.179314131248</v>
+      </c>
+      <c r="I29" s="26">
+        <v>6598.784626525</v>
+      </c>
+      <c r="J29" s="26">
+        <v>4.2678183947677422</v>
+      </c>
+      <c r="K29" s="27">
+        <f t="shared" si="1"/>
+        <v>18071.993409070794</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="32">
+        <v>0</v>
+      </c>
+      <c r="E30" s="26">
+        <v>0</v>
+      </c>
+      <c r="F30" s="25">
+        <v>6.5873503048004141</v>
+      </c>
+      <c r="G30" s="26">
+        <v>308.06809025333331</v>
+      </c>
+      <c r="H30" s="25">
+        <v>10855.051409156249</v>
+      </c>
+      <c r="I30" s="26">
+        <v>6502.1258073718755</v>
+      </c>
+      <c r="J30" s="26">
+        <v>4.3627703926133332</v>
+      </c>
+      <c r="K30" s="27">
+        <f t="shared" si="1"/>
+        <v>17676.195427478873</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="32">
+        <v>0</v>
+      </c>
+      <c r="E31" s="26"/>
+      <c r="F31" s="25">
+        <v>6.5685155999999996</v>
+      </c>
+      <c r="G31" s="26">
+        <v>311.71525303419355</v>
+      </c>
+      <c r="H31" s="25">
+        <v>10899.427514799998</v>
+      </c>
+      <c r="I31" s="26">
+        <v>6877.3351555124991</v>
+      </c>
+      <c r="J31" s="26">
+        <v>4.5149624965548387</v>
+      </c>
+      <c r="K31" s="27">
+        <f t="shared" si="1"/>
+        <v>18099.561401443247</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="32">
+        <v>0</v>
+      </c>
+      <c r="E32" s="26"/>
+      <c r="F32" s="25">
+        <v>5.9834704292572019</v>
+      </c>
+      <c r="G32" s="26">
+        <v>312.78317792999997</v>
+      </c>
+      <c r="H32" s="25">
+        <v>11361.611756625</v>
+      </c>
+      <c r="I32" s="26">
+        <v>6854.9407329968753</v>
+      </c>
+      <c r="J32" s="26">
+        <v>4.8860221122</v>
+      </c>
+      <c r="K32" s="27">
+        <f t="shared" si="1"/>
+        <v>18540.205160093334</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="32">
+        <v>0</v>
+      </c>
+      <c r="E33" s="26"/>
+      <c r="F33" s="25">
+        <v>5.9761414211608885</v>
+      </c>
+      <c r="G33" s="26">
+        <v>312.50607223806458</v>
+      </c>
+      <c r="H33" s="25">
+        <v>11407.0991685875</v>
+      </c>
+      <c r="I33" s="26">
+        <v>7049.0650891968744</v>
+      </c>
+      <c r="J33" s="26">
+        <v>5.5040800145096771</v>
+      </c>
+      <c r="K33" s="27">
+        <f t="shared" si="1"/>
+        <v>18780.150551458111</v>
+      </c>
+    </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B34" s="18">
-        <v>2023</v>
-      </c>
-      <c r="C34" s="18" t="s">
+      <c r="B34" s="17">
+        <v>2024</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="37">
-        <v>0</v>
-      </c>
-      <c r="E34" s="30">
-        <v>8.9783383367741934</v>
-      </c>
-      <c r="F34" s="28">
-        <v>5.9225999482208254</v>
-      </c>
-      <c r="G34" s="30">
-        <v>300.50389279677415</v>
-      </c>
-      <c r="H34" s="28">
-        <v>11072.679838818749</v>
-      </c>
-      <c r="I34" s="30">
-        <v>6639.4135220343742</v>
-      </c>
-      <c r="J34" s="30">
-        <v>4.8295796983645163</v>
-      </c>
-      <c r="K34" s="31">
-        <f t="shared" si="0"/>
-        <v>18032.32777163326</v>
+      <c r="D34" s="32"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="25">
+        <v>5.2425093811798087</v>
+      </c>
+      <c r="G34" s="26">
+        <v>288.40670568967738</v>
+      </c>
+      <c r="H34" s="25">
+        <v>10774.092688656248</v>
+      </c>
+      <c r="I34" s="26">
+        <v>7004.6122846562494</v>
+      </c>
+      <c r="J34" s="26"/>
+      <c r="K34" s="27">
+        <f t="shared" si="1"/>
+        <v>18072.354188383353</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B35" s="18"/>
-      <c r="C35" s="18" t="s">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="37">
-        <v>0</v>
-      </c>
-      <c r="E35" s="30">
-        <v>9.0995634314285709</v>
-      </c>
-      <c r="F35" s="28">
-        <v>5.4081785888977052</v>
-      </c>
-      <c r="G35" s="30">
-        <v>309.58417966428573</v>
-      </c>
-      <c r="H35" s="28">
-        <v>11120.41634936875</v>
-      </c>
-      <c r="I35" s="30">
-        <v>6508.3963560343755</v>
-      </c>
-      <c r="J35" s="30">
-        <v>4.8211832453642858</v>
-      </c>
-      <c r="K35" s="31">
-        <f t="shared" si="0"/>
-        <v>17957.725810333101</v>
-      </c>
+      <c r="D35" s="32"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="25">
+        <v>5.5273438095764158</v>
+      </c>
+      <c r="G35" s="26">
+        <v>309.95271274000004</v>
+      </c>
+      <c r="H35" s="25">
+        <v>11146.104410125001</v>
+      </c>
+      <c r="I35" s="26">
+        <v>7168.5244487656246</v>
+      </c>
+      <c r="J35" s="26"/>
+      <c r="K35" s="27"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B36" s="18"/>
-      <c r="C36" s="18" t="s">
+      <c r="B36" s="17"/>
+      <c r="C36" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="D36" s="37">
-        <v>0</v>
-      </c>
-      <c r="E36" s="30">
-        <v>7.4471656316129025</v>
-      </c>
-      <c r="F36" s="28">
-        <v>5.7642538211608878</v>
-      </c>
-      <c r="G36" s="30">
-        <v>304.09686855161283</v>
-      </c>
-      <c r="H36" s="28">
-        <v>11063.495835656249</v>
-      </c>
-      <c r="I36" s="30">
-        <v>6719.7404422687496</v>
-      </c>
-      <c r="J36" s="30">
-        <v>4.641218457048387</v>
-      </c>
-      <c r="K36" s="31">
-        <f t="shared" si="0"/>
-        <v>18105.185784386431</v>
-      </c>
+      <c r="D36" s="32"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="25">
+        <v>5.7710892352996828</v>
+      </c>
+      <c r="G36" s="26"/>
+      <c r="H36" s="25">
+        <v>11115.963399025</v>
+      </c>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="27"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B37" s="18"/>
-      <c r="C37" s="18" t="s">
+      <c r="B37" s="17"/>
+      <c r="C37" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="37">
-        <v>0</v>
-      </c>
-      <c r="E37" s="30">
-        <v>3.2335224913333329</v>
-      </c>
-      <c r="F37" s="28">
-        <v>6.2412671170288085</v>
-      </c>
-      <c r="G37" s="30">
-        <v>319.64939560800002</v>
-      </c>
-      <c r="H37" s="28">
-        <v>11090.713460024999</v>
-      </c>
-      <c r="I37" s="30">
-        <v>6823.3087836281247</v>
-      </c>
-      <c r="J37" s="30">
-        <v>5.2265925831399995</v>
-      </c>
-      <c r="K37" s="31">
-        <f t="shared" ref="K37:K42" si="1">SUM(D37:J37)</f>
-        <v>18248.373021452626</v>
-      </c>
+      <c r="D37" s="32"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="25">
+        <v>11138.4654207125</v>
+      </c>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="27"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B38" s="18"/>
-      <c r="C38" s="18" t="s">
+      <c r="B38" s="17"/>
+      <c r="C38" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="37">
-        <v>0</v>
-      </c>
-      <c r="E38" s="30">
-        <v>0.26508733612903224</v>
-      </c>
-      <c r="F38" s="28">
-        <v>6.3281482752807614</v>
-      </c>
-      <c r="G38" s="30">
-        <v>313.13831749612905</v>
-      </c>
-      <c r="H38" s="28">
-        <v>9693.7473418749996</v>
-      </c>
-      <c r="I38" s="30">
-        <v>6550.4025209437505</v>
-      </c>
-      <c r="J38" s="30">
-        <v>4.9269568599129032</v>
-      </c>
-      <c r="K38" s="31">
-        <f t="shared" si="1"/>
-        <v>16568.808372786199</v>
-      </c>
+      <c r="D38" s="32"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="27"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B39" s="18"/>
-      <c r="C39" s="18" t="s">
+      <c r="B39" s="17"/>
+      <c r="C39" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D39" s="37">
-        <v>0</v>
-      </c>
-      <c r="E39" s="30">
-        <v>0</v>
-      </c>
-      <c r="F39" s="28">
-        <v>6.3872340585144043</v>
-      </c>
-      <c r="G39" s="30">
-        <v>305.52049500933333</v>
-      </c>
-      <c r="H39" s="28">
-        <v>10340.548587431251</v>
-      </c>
-      <c r="I39" s="30">
-        <v>6382.8866122624995</v>
-      </c>
-      <c r="J39" s="30">
-        <v>5.3461842988866675</v>
-      </c>
-      <c r="K39" s="31">
-        <f t="shared" si="1"/>
-        <v>17040.689113060485</v>
-      </c>
+      <c r="D39" s="32"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="27"/>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B40" s="18"/>
-      <c r="C40" s="18" t="s">
+      <c r="B40" s="17"/>
+      <c r="C40" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="37">
-        <v>0</v>
-      </c>
-      <c r="E40" s="30">
-        <v>0</v>
-      </c>
-      <c r="F40" s="28">
-        <v>6.3999166211608882</v>
-      </c>
-      <c r="G40" s="30">
-        <v>315.38990804129025</v>
-      </c>
-      <c r="H40" s="28">
-        <v>11073.1687253125</v>
-      </c>
-      <c r="I40" s="30">
-        <v>6607.0443803906255</v>
-      </c>
-      <c r="J40" s="30">
-        <v>4.8875286786032257</v>
-      </c>
-      <c r="K40" s="31">
-        <f t="shared" si="1"/>
-        <v>18006.890459044178</v>
-      </c>
+      <c r="D40" s="32"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="27"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B41" s="18"/>
-      <c r="C41" s="20" t="s">
+      <c r="B41" s="17"/>
+      <c r="C41" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D41" s="37"/>
-      <c r="E41" s="30">
-        <v>0</v>
-      </c>
-      <c r="F41" s="28">
-        <v>6.6004127623596185</v>
-      </c>
-      <c r="G41" s="30">
-        <v>309.47425686903222</v>
-      </c>
-      <c r="H41" s="28">
-        <v>11117.38370809375</v>
-      </c>
-      <c r="I41" s="30">
-        <v>6598.784626525</v>
-      </c>
-      <c r="J41" s="30"/>
-      <c r="K41" s="31">
-        <f t="shared" si="1"/>
-        <v>18032.243004250144</v>
-      </c>
+      <c r="D41" s="32"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="27"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B42" s="18"/>
-      <c r="C42" s="18" t="s">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="37"/>
-      <c r="E42" s="30">
-        <v>0</v>
-      </c>
-      <c r="F42" s="28">
-        <v>6.5873503048004141</v>
-      </c>
-      <c r="G42" s="30">
-        <v>309.48514743599998</v>
-      </c>
-      <c r="H42" s="28">
-        <v>10808.116098593749</v>
-      </c>
-      <c r="I42" s="30">
-        <v>6502.1258073718755</v>
-      </c>
-      <c r="J42" s="30"/>
-      <c r="K42" s="31">
-        <f t="shared" si="1"/>
-        <v>17626.314403706427</v>
-      </c>
+      <c r="D42" s="32"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="27"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B43" s="18"/>
-      <c r="C43" s="18" t="s">
+      <c r="B43" s="17"/>
+      <c r="C43" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D43" s="37"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="28">
-        <v>10868.21823705</v>
-      </c>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="31"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="27"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B44" s="18"/>
-      <c r="C44" s="18" t="s">
+      <c r="B44" s="17"/>
+      <c r="C44" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D44" s="37"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="28"/>
-      <c r="I44" s="30"/>
-      <c r="J44" s="30"/>
-      <c r="K44" s="31"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="27"/>
     </row>
     <row r="45" spans="2:11" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="21"/>
-      <c r="C45" s="21" t="s">
+      <c r="B45" s="20"/>
+      <c r="C45" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="D45" s="38"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="40"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="40"/>
-      <c r="I45" s="39"/>
-      <c r="J45" s="39"/>
-      <c r="K45" s="41"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="36"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="C46" s="23"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="59" t="s">
+      <c r="C46" s="22"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="K46" s="60">
-        <v>45295</v>
+      <c r="K46" s="54">
+        <v>45448</v>
       </c>
     </row>
   </sheetData>
@@ -5998,7 +5669,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="5.140625" customWidth="1"/>
@@ -12945,7 +12616,7 @@
         <v>182.36379032258063</v>
       </c>
       <c r="K240" s="1">
-        <f t="shared" ref="K240:K296" si="5">SUM(C240:I240)</f>
+        <f t="shared" ref="K240:K300" si="5">SUM(C240:I240)</f>
         <v>453767.596048387</v>
       </c>
     </row>
@@ -14373,10 +14044,10 @@
         <v>167.70967102050781</v>
       </c>
       <c r="F288" s="1">
-        <v>8509.3387096774186</v>
+        <v>8522.9064516129019</v>
       </c>
       <c r="G288" s="1">
-        <v>313543.96875</v>
+        <v>313561.78125</v>
       </c>
       <c r="H288" s="1">
         <v>188007.609375</v>
@@ -14386,7 +14057,7 @@
       </c>
       <c r="K288" s="1">
         <f t="shared" si="5"/>
-        <v>510619.62394118175</v>
+        <v>510651.00418311724</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.2">
@@ -14403,10 +14074,10 @@
         <v>153.14285278320313</v>
       </c>
       <c r="F289" s="1">
-        <v>8766.4642857142862</v>
+        <v>8767.9357142857134</v>
       </c>
       <c r="G289" s="1">
-        <v>314895.71875</v>
+        <v>314904.96875</v>
       </c>
       <c r="H289" s="1">
         <v>184297.609375</v>
@@ -14416,7 +14087,7 @@
       </c>
       <c r="K289" s="1">
         <f t="shared" si="5"/>
-        <v>508507.12765635463</v>
+        <v>508517.84908492607</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.2">
@@ -14433,10 +14104,10 @@
         <v>163.22579956054688</v>
       </c>
       <c r="F290" s="1">
-        <v>8611.0806451612898</v>
+        <v>8588.6419354838708</v>
       </c>
       <c r="G290" s="1">
-        <v>313283.90625</v>
+        <v>313318.1875</v>
       </c>
       <c r="H290" s="1">
         <v>190282.21875</v>
@@ -14446,7 +14117,7 @@
       </c>
       <c r="K290" s="1">
         <f t="shared" si="5"/>
-        <v>512682.73700923799</v>
+        <v>512694.57954956056</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.2">
@@ -14463,10 +14134,10 @@
         <v>176.73333740234375</v>
       </c>
       <c r="F291" s="1">
-        <v>9051.4800000000014</v>
+        <v>9023.3966666666674</v>
       </c>
       <c r="G291" s="1">
-        <v>314054.625</v>
+        <v>314085.46875</v>
       </c>
       <c r="H291" s="1">
         <v>193214.953125</v>
@@ -14476,7 +14147,7 @@
       </c>
       <c r="K291" s="1">
         <f t="shared" si="5"/>
-        <v>516737.35569573566</v>
+        <v>516740.11611240235</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.2">
@@ -14493,10 +14164,10 @@
         <v>179.19354248046875</v>
       </c>
       <c r="F292" s="1">
-        <v>8867.1064516129027</v>
+        <v>8840.1935483870966</v>
       </c>
       <c r="G292" s="1">
-        <v>274496.875</v>
+        <v>274588.1875</v>
       </c>
       <c r="H292" s="1">
         <v>185487.09375</v>
@@ -14506,7 +14177,7 @@
       </c>
       <c r="K292" s="1">
         <f t="shared" si="5"/>
-        <v>469177.29134086758</v>
+        <v>469241.69093764178</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.2">
@@ -14523,10 +14194,10 @@
         <v>180.86666870117188</v>
       </c>
       <c r="F293" s="1">
-        <v>8651.3933333333334</v>
+        <v>8627.1299999999992</v>
       </c>
       <c r="G293" s="1">
-        <v>292812.28125</v>
+        <v>292851.0625</v>
       </c>
       <c r="H293" s="1">
         <v>180743.5625</v>
@@ -14536,7 +14207,7 @@
       </c>
       <c r="K293" s="1">
         <f t="shared" si="5"/>
-        <v>482539.49111870117</v>
+        <v>482554.00903536787</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.2">
@@ -14553,10 +14224,10 @@
         <v>181.22579956054688</v>
       </c>
       <c r="F294" s="1">
-        <v>8930.8645161290315</v>
+        <v>8897.145161290322</v>
       </c>
       <c r="G294" s="1">
-        <v>313557.8125</v>
+        <v>313778.25</v>
       </c>
       <c r="H294" s="1">
         <v>187091.015625</v>
@@ -14566,13 +14237,16 @@
       </c>
       <c r="K294" s="1">
         <f t="shared" si="5"/>
-        <v>509899.31810197991</v>
+        <v>510086.03624714119</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>45139</v>
       </c>
+      <c r="C295" s="1">
+        <v>0</v>
+      </c>
       <c r="D295" s="1">
         <v>0</v>
       </c>
@@ -14580,23 +14254,29 @@
         <v>186.90322875976563</v>
       </c>
       <c r="F295" s="1">
-        <v>8763.351612903225</v>
+        <v>8726.1709677419349</v>
       </c>
       <c r="G295" s="1">
-        <v>314809.84375</v>
+        <v>315851.78125</v>
       </c>
       <c r="H295" s="1">
         <v>186857.125</v>
       </c>
+      <c r="I295" s="1">
+        <v>120.8513870967742</v>
+      </c>
       <c r="K295" s="1">
         <f t="shared" si="5"/>
-        <v>510617.223591663</v>
+        <v>511742.83183359849</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>45170</v>
       </c>
+      <c r="C296" s="1">
+        <v>0</v>
+      </c>
       <c r="D296" s="1">
         <v>0</v>
       </c>
@@ -14604,35 +14284,198 @@
         <v>186.53334045410156</v>
       </c>
       <c r="F296" s="1">
-        <v>8763.66</v>
+        <v>8723.5333333333328</v>
       </c>
       <c r="G296" s="1">
-        <v>306052.34375</v>
+        <v>307381.40625</v>
       </c>
       <c r="H296" s="1">
         <v>184120.046875</v>
       </c>
+      <c r="I296" s="1">
+        <v>123.54013333333334</v>
+      </c>
       <c r="K296" s="1">
         <f t="shared" si="5"/>
-        <v>499122.58396545408</v>
+        <v>500535.05993212078</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>45200</v>
       </c>
+      <c r="C297" s="1">
+        <v>0</v>
+      </c>
+      <c r="E297" s="1">
+        <v>186</v>
+      </c>
+      <c r="F297" s="1">
+        <v>8826.8096774193546</v>
+      </c>
       <c r="G297" s="1">
-        <v>307754.25</v>
+        <v>308638</v>
+      </c>
+      <c r="H297" s="1">
+        <v>194744.8125</v>
+      </c>
+      <c r="I297" s="1">
+        <v>127.84974193548386</v>
+      </c>
+      <c r="K297" s="1">
+        <f t="shared" si="5"/>
+        <v>512523.47191935487</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>45231</v>
       </c>
+      <c r="C298" s="1">
+        <v>0</v>
+      </c>
+      <c r="E298" s="1">
+        <v>169.43333435058594</v>
+      </c>
+      <c r="F298" s="1">
+        <v>8857.0499999999993</v>
+      </c>
+      <c r="G298" s="1">
+        <v>321725.625</v>
+      </c>
+      <c r="H298" s="1">
+        <v>194110.671875</v>
+      </c>
+      <c r="I298" s="1">
+        <v>138.357</v>
+      </c>
+      <c r="K298" s="1">
+        <f t="shared" si="5"/>
+        <v>525001.13720935059</v>
+      </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>45261</v>
+      </c>
+      <c r="C299" s="1">
+        <v>0</v>
+      </c>
+      <c r="E299" s="1">
+        <v>169.22579956054688</v>
+      </c>
+      <c r="F299" s="1">
+        <v>8849.2032258064537</v>
+      </c>
+      <c r="G299" s="1">
+        <v>323013.6875</v>
+      </c>
+      <c r="H299" s="1">
+        <v>199607.671875</v>
+      </c>
+      <c r="I299" s="1">
+        <v>155.85848387096775</v>
+      </c>
+      <c r="K299" s="1">
+        <f t="shared" si="5"/>
+        <v>531795.646884238</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A300" s="6">
+        <v>45292</v>
+      </c>
+      <c r="E300" s="1">
+        <v>148.45161437988281</v>
+      </c>
+      <c r="F300" s="1">
+        <v>8166.7838709677417</v>
+      </c>
+      <c r="G300" s="1">
+        <v>305088.90625</v>
+      </c>
+      <c r="H300" s="1">
+        <v>198348.90625</v>
+      </c>
+      <c r="K300" s="1">
+        <f t="shared" si="5"/>
+        <v>511753.04798534763</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A301" s="6">
+        <v>45323</v>
+      </c>
+      <c r="E301" s="1">
+        <v>156.51724243164063</v>
+      </c>
+      <c r="F301" s="1">
+        <v>8776.9000000000015</v>
+      </c>
+      <c r="G301" s="1">
+        <v>315623.125</v>
+      </c>
+      <c r="H301" s="1">
+        <v>202990.390625</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A302" s="6">
+        <v>45352</v>
+      </c>
+      <c r="E302" s="1">
+        <v>163.41935729980469</v>
+      </c>
+      <c r="G302" s="1">
+        <v>314769.625</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A303" s="6">
+        <v>45383</v>
+      </c>
+      <c r="G303" s="1">
+        <v>315406.8125</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A304" s="6">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A305" s="6">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A306" s="6">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A307" s="6">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A308" s="6">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A309" s="6">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A310" s="6">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A311" s="6">
+        <v>45627</v>
       </c>
     </row>
   </sheetData>
@@ -14642,7 +14485,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M311"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="5.140625" customWidth="1"/>
@@ -21102,11 +20945,11 @@
       <c r="H228" s="1">
         <v>5212.7357036903222</v>
       </c>
-      <c r="I228" s="25">
+      <c r="I228" s="24">
         <v>0.47650217616129031</v>
       </c>
       <c r="K228" s="1">
-        <f t="shared" ref="K228:K296" si="5">SUM(C228:I228)</f>
+        <f t="shared" ref="K228:K297" si="5">SUM(C228:I228)</f>
         <v>16520.729929684676</v>
       </c>
       <c r="M228" s="2" t="s">
@@ -21135,7 +20978,7 @@
       <c r="H229" s="1">
         <v>5199.0010339128567</v>
       </c>
-      <c r="I229" s="25">
+      <c r="I229" s="24">
         <v>0.13143967996428571</v>
       </c>
       <c r="K229" s="1">
@@ -21165,7 +21008,7 @@
       <c r="H230" s="1">
         <v>5250.0212001245163</v>
       </c>
-      <c r="I230" s="25">
+      <c r="I230" s="24">
         <v>1.8181323096774196E-2</v>
       </c>
       <c r="K230" s="1">
@@ -21195,7 +21038,7 @@
       <c r="H231" s="1">
         <v>5296.7756420266669</v>
       </c>
-      <c r="I231" s="25">
+      <c r="I231" s="24">
         <v>0.2877374750333333</v>
       </c>
       <c r="K231" s="1">
@@ -21225,7 +21068,7 @@
       <c r="H232" s="1">
         <v>5053.6240646193546</v>
       </c>
-      <c r="I232" s="25">
+      <c r="I232" s="24">
         <v>0.29479716735483869</v>
       </c>
       <c r="K232" s="1">
@@ -21255,7 +21098,7 @@
       <c r="H233" s="1">
         <v>5031.8430408046715</v>
       </c>
-      <c r="I233" s="25">
+      <c r="I233" s="24">
         <v>0.34264579226666664</v>
       </c>
       <c r="K233" s="1">
@@ -21285,7 +21128,7 @@
       <c r="H234" s="1">
         <v>5317.6991248271015</v>
       </c>
-      <c r="I234" s="25">
+      <c r="I234" s="24">
         <v>0.17012523754838707</v>
       </c>
       <c r="K234" s="1">
@@ -21315,7 +21158,7 @@
       <c r="H235" s="1">
         <v>5157.9656070419296</v>
       </c>
-      <c r="I235" s="25">
+      <c r="I235" s="24">
         <v>0.130515926516129</v>
       </c>
       <c r="K235" s="1">
@@ -21345,7 +21188,7 @@
       <c r="H236" s="1">
         <v>5175.1241433773357</v>
       </c>
-      <c r="I236" s="25">
+      <c r="I236" s="24">
         <v>0.18563708066666665</v>
       </c>
       <c r="K236" s="1">
@@ -21375,7 +21218,7 @@
       <c r="H237" s="1">
         <v>4701.9891877451673</v>
       </c>
-      <c r="I237" s="25">
+      <c r="I237" s="24">
         <v>1.3715512827516134</v>
       </c>
       <c r="K237" s="1">
@@ -22901,10 +22744,10 @@
         <v>5.9225999482208254</v>
       </c>
       <c r="F288" s="1">
-        <v>300.50389279677415</v>
+        <v>300.98303217612897</v>
       </c>
       <c r="G288" s="1">
-        <v>11072.679838818749</v>
+        <v>11073.30888013125</v>
       </c>
       <c r="H288" s="1">
         <v>6639.4135220343742</v>
@@ -22914,7 +22757,7 @@
       </c>
       <c r="K288" s="1">
         <f t="shared" si="5"/>
-        <v>18032.32777163326</v>
+        <v>18033.435952325111</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.2">
@@ -22931,10 +22774,10 @@
         <v>5.4081785888977052</v>
       </c>
       <c r="F289" s="1">
-        <v>309.58417966428573</v>
+        <v>309.63614257571425</v>
       </c>
       <c r="G289" s="1">
-        <v>11120.41634936875</v>
+        <v>11120.743009418751</v>
       </c>
       <c r="H289" s="1">
         <v>6508.3963560343755</v>
@@ -22944,7 +22787,7 @@
       </c>
       <c r="K289" s="1">
         <f t="shared" si="5"/>
-        <v>17957.725810333101</v>
+        <v>17958.104433294531</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.2">
@@ -22961,10 +22804,10 @@
         <v>5.7642538211608878</v>
       </c>
       <c r="F290" s="1">
-        <v>304.09686855161283</v>
+        <v>303.30445449483869</v>
       </c>
       <c r="G290" s="1">
-        <v>11063.495835656249</v>
+        <v>11064.706464287501</v>
       </c>
       <c r="H290" s="1">
         <v>6719.7404422687496</v>
@@ -22974,7 +22817,7 @@
       </c>
       <c r="K290" s="1">
         <f t="shared" si="5"/>
-        <v>18105.185784386431</v>
+        <v>18105.603998960909</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.2">
@@ -22991,10 +22834,10 @@
         <v>6.2412671170288085</v>
       </c>
       <c r="F291" s="1">
-        <v>319.64939560800002</v>
+        <v>318.65764392466667</v>
       </c>
       <c r="G291" s="1">
-        <v>11090.713460024999</v>
+        <v>11091.80269471875</v>
       </c>
       <c r="H291" s="1">
         <v>6823.3087836281247</v>
@@ -23004,7 +22847,7 @@
       </c>
       <c r="K291" s="1">
         <f t="shared" si="5"/>
-        <v>18248.373021452626</v>
+        <v>18248.470504463043</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.2">
@@ -23021,10 +22864,10 @@
         <v>6.3281482752807614</v>
       </c>
       <c r="F292" s="1">
-        <v>313.13831749612905</v>
+        <v>312.18789908387095</v>
       </c>
       <c r="G292" s="1">
-        <v>9693.7473418749996</v>
+        <v>9696.9720062875003</v>
       </c>
       <c r="H292" s="1">
         <v>6550.4025209437505</v>
@@ -23034,7 +22877,7 @@
       </c>
       <c r="K292" s="1">
         <f t="shared" si="5"/>
-        <v>16568.808372786199</v>
+        <v>16571.082618786444</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.2">
@@ -23051,10 +22894,10 @@
         <v>6.3872340585144043</v>
       </c>
       <c r="F293" s="1">
-        <v>305.52049500933333</v>
+        <v>304.66364509799996</v>
       </c>
       <c r="G293" s="1">
-        <v>10340.548587431251</v>
+        <v>10341.918131762501</v>
       </c>
       <c r="H293" s="1">
         <v>6382.8866122624995</v>
@@ -23064,7 +22907,7 @@
       </c>
       <c r="K293" s="1">
         <f t="shared" si="5"/>
-        <v>17040.689113060485</v>
+        <v>17041.201807480404</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.2">
@@ -23081,10 +22924,10 @@
         <v>6.3999166211608882</v>
       </c>
       <c r="F294" s="1">
-        <v>315.38990804129025</v>
+        <v>314.19912251290316</v>
       </c>
       <c r="G294" s="1">
-        <v>11073.1687253125</v>
+        <v>11080.953387449999</v>
       </c>
       <c r="H294" s="1">
         <v>6607.0443803906255</v>
@@ -23094,13 +22937,16 @@
       </c>
       <c r="K294" s="1">
         <f t="shared" si="5"/>
-        <v>18006.890459044178</v>
+        <v>18013.484335653291</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="6">
         <v>45139</v>
       </c>
+      <c r="C295" s="1">
+        <v>0</v>
+      </c>
       <c r="D295" s="1">
         <v>0</v>
       </c>
@@ -23108,23 +22954,29 @@
         <v>6.6004127623596185</v>
       </c>
       <c r="F295" s="1">
-        <v>309.47425686903222</v>
+        <v>308.16123725741932</v>
       </c>
       <c r="G295" s="1">
-        <v>11117.38370809375</v>
+        <v>11154.179314131248</v>
       </c>
       <c r="H295" s="1">
         <v>6598.784626525</v>
       </c>
+      <c r="I295" s="1">
+        <v>4.2678183947677422</v>
+      </c>
       <c r="K295" s="1">
         <f t="shared" si="5"/>
-        <v>18032.243004250144</v>
+        <v>18071.993409070794</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="6">
         <v>45170</v>
       </c>
+      <c r="C296" s="1">
+        <v>0</v>
+      </c>
       <c r="D296" s="1">
         <v>0</v>
       </c>
@@ -23132,35 +22984,198 @@
         <v>6.5873503048004141</v>
       </c>
       <c r="F296" s="1">
-        <v>309.48514743599998</v>
+        <v>308.06809025333331</v>
       </c>
       <c r="G296" s="1">
-        <v>10808.116098593749</v>
+        <v>10855.051409156249</v>
       </c>
       <c r="H296" s="1">
         <v>6502.1258073718755</v>
       </c>
+      <c r="I296" s="1">
+        <v>4.3627703926133332</v>
+      </c>
       <c r="K296" s="1">
         <f t="shared" si="5"/>
-        <v>17626.314403706427</v>
+        <v>17676.195427478873</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="6">
         <v>45200</v>
       </c>
+      <c r="C297" s="1">
+        <v>0</v>
+      </c>
+      <c r="E297" s="1">
+        <v>6.5685155999999996</v>
+      </c>
+      <c r="F297" s="1">
+        <v>311.71525303419355</v>
+      </c>
       <c r="G297" s="1">
-        <v>10868.21823705</v>
+        <v>10899.427514799998</v>
+      </c>
+      <c r="H297" s="1">
+        <v>6877.3351555124991</v>
+      </c>
+      <c r="I297" s="1">
+        <v>4.5149624965548387</v>
+      </c>
+      <c r="K297" s="1">
+        <f t="shared" si="5"/>
+        <v>18099.561401443247</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="6">
         <v>45231</v>
       </c>
+      <c r="C298" s="1">
+        <v>0</v>
+      </c>
+      <c r="E298" s="1">
+        <v>5.9834704292572019</v>
+      </c>
+      <c r="F298" s="1">
+        <v>312.78317792999997</v>
+      </c>
+      <c r="G298" s="1">
+        <v>11361.611756625</v>
+      </c>
+      <c r="H298" s="1">
+        <v>6854.9407329968753</v>
+      </c>
+      <c r="I298" s="1">
+        <v>4.8860221122</v>
+      </c>
+      <c r="K298" s="1">
+        <f t="shared" ref="K298:K300" si="6">SUM(C298:I298)</f>
+        <v>18540.205160093334</v>
+      </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="6">
         <v>45261</v>
+      </c>
+      <c r="C299" s="1">
+        <v>0</v>
+      </c>
+      <c r="E299" s="1">
+        <v>5.9761414211608885</v>
+      </c>
+      <c r="F299" s="1">
+        <v>312.50607223806458</v>
+      </c>
+      <c r="G299" s="1">
+        <v>11407.0991685875</v>
+      </c>
+      <c r="H299" s="1">
+        <v>7049.0650891968744</v>
+      </c>
+      <c r="I299" s="1">
+        <v>5.5040800145096771</v>
+      </c>
+      <c r="K299" s="1">
+        <f t="shared" si="6"/>
+        <v>18780.150551458111</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A300" s="6">
+        <v>45292</v>
+      </c>
+      <c r="E300" s="1">
+        <v>5.2425093811798087</v>
+      </c>
+      <c r="F300" s="1">
+        <v>288.40670568967738</v>
+      </c>
+      <c r="G300" s="1">
+        <v>10774.092688656248</v>
+      </c>
+      <c r="H300" s="1">
+        <v>7004.6122846562494</v>
+      </c>
+      <c r="K300" s="1">
+        <f t="shared" si="6"/>
+        <v>18072.354188383353</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A301" s="6">
+        <v>45323</v>
+      </c>
+      <c r="E301" s="1">
+        <v>5.5273438095764158</v>
+      </c>
+      <c r="F301" s="1">
+        <v>309.95271274000004</v>
+      </c>
+      <c r="G301" s="1">
+        <v>11146.104410125001</v>
+      </c>
+      <c r="H301" s="1">
+        <v>7168.5244487656246</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A302" s="6">
+        <v>45352</v>
+      </c>
+      <c r="E302" s="1">
+        <v>5.7710892352996828</v>
+      </c>
+      <c r="G302" s="1">
+        <v>11115.963399025</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A303" s="6">
+        <v>45383</v>
+      </c>
+      <c r="G303" s="1">
+        <v>11138.4654207125</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A304" s="6">
+        <v>45413</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A305" s="6">
+        <v>45444</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A306" s="6">
+        <v>45474</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A307" s="6">
+        <v>45505</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A308" s="6">
+        <v>45536</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A309" s="6">
+        <v>45566</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A310" s="6">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A311" s="6">
+        <v>45627</v>
       </c>
     </row>
   </sheetData>
@@ -23169,8 +23184,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CEF22DAF496ADE498A94ECACB103F1AD" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="94ca56df59429f33e9578fc51d07b71b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee349bb3-f777-4768-a131-ca5c9eb9e69a" xmlns:ns3="615a73cf-3ca8-4f1d-9e40-da9305ba6dc8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9a936563a2c046556d5fbda508711cd0" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CEF22DAF496ADE498A94ECACB103F1AD" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5c663b3284d4c5f5094bc61340bea10c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ee349bb3-f777-4768-a131-ca5c9eb9e69a" xmlns:ns3="615a73cf-3ca8-4f1d-9e40-da9305ba6dc8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="54caa06515303bb7efed8fa8993adb8e" ns2:_="" ns3:_="">
     <xsd:import namespace="ee349bb3-f777-4768-a131-ca5c9eb9e69a"/>
     <xsd:import namespace="615a73cf-3ca8-4f1d-9e40-da9305ba6dc8"/>
     <xsd:element name="properties">
@@ -23192,6 +23207,7 @@
                 <xsd:element ref="ns2:Key" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -23267,6 +23283,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -23396,7 +23417,7 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <parentID xmlns="ee349bb3-f777-4768-a131-ca5c9eb9e69a">1109</parentID>
+    <parentID xmlns="ee349bb3-f777-4768-a131-ca5c9eb9e69a">1687</parentID>
     <Key xmlns="ee349bb3-f777-4768-a131-ca5c9eb9e69a">0</Key>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="ee349bb3-f777-4768-a131-ca5c9eb9e69a">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -23408,45 +23429,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBBB026C-2114-45DE-92A2-4291C996E22B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ee349bb3-f777-4768-a131-ca5c9eb9e69a"/>
-    <ds:schemaRef ds:uri="615a73cf-3ca8-4f1d-9e40-da9305ba6dc8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE2CF7CF-C82C-41BE-8115-4446ED2B39F6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36C70269-AA85-4252-8748-F469E573FBB1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5F92436-45F5-4404-9513-D9AEF1C33817}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B83C2F70-3E90-457E-9657-392B8136BCE1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ee349bb3-f777-4768-a131-ca5c9eb9e69a"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="615a73cf-3ca8-4f1d-9e40-da9305ba6dc8"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6107405-F225-4EE3-B0B1-331359720F7A}"/>
 </file>